--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AF3B41-7E57-4BF4-A42E-3C53ED0CB46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B7EFD4-41C5-4454-94C8-AA6B77AF3092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="225">
   <si>
     <t>Key</t>
   </si>
@@ -607,15 +607,9 @@
     <t>[ 5I.10.54.12.16 ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
     <t>[ 4A.43.04 ]</t>
   </si>
   <si>
-    <t>[ IfcZone ]</t>
-  </si>
-  <si>
     <t>[ 4U.74 ]</t>
   </si>
   <si>
@@ -746,9 +740,6 @@
   </si>
   <si>
     <t>SUS.Informação</t>
-  </si>
-  <si>
-    <t>[ OST_Areas : OST_Rooms : OST_MEPSpaces ]</t>
   </si>
   <si>
     <t>[ OST_Areas : OST_Rooms : OST_MEPSpaces : OST_MEPZone ]</t>
@@ -1243,41 +1234,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -1443,6 +1400,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1778,14 +1753,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.3828125" customWidth="1"/>
+    <col min="2" max="2" width="48.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -1796,7 +1771,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
@@ -1807,7 +1782,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -1818,7 +1793,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -1829,7 +1804,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -1841,7 +1816,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -1853,7 +1828,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -1864,7 +1839,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
@@ -1875,7 +1850,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -1886,7 +1861,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -1897,7 +1872,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -1908,7 +1883,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -1919,7 +1894,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -1930,7 +1905,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -1941,7 +1916,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -1952,7 +1927,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -1963,7 +1938,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -1974,19 +1949,19 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46244.499835069444</v>
+        <v>46249.44650150463</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -1997,7 +1972,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2008,7 +1983,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>172</v>
       </c>
@@ -2019,7 +1994,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>169</v>
       </c>
@@ -2031,7 +2006,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>173</v>
       </c>
@@ -2043,7 +2018,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
@@ -2054,7 +2029,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
@@ -2065,7 +2040,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>162</v>
       </c>
@@ -2077,155 +2052,155 @@
         <v>167</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B30" s="52" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B32" s="52" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B35" s="52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C38" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B39" s="54" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C39" s="36" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" s="49" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C40" s="36" t="s">
         <v>165</v>
@@ -2248,35 +2223,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="47.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="1.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.53515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="35.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="25.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.07421875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="34.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="36.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2359,12 +2334,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="40">
         <v>2</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>14</v>
@@ -2373,7 +2348,7 @@
         <v>128</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F2" s="58" t="s">
         <v>95</v>
@@ -2431,17 +2406,17 @@
         <v>SUS.Volume</v>
       </c>
       <c r="V2" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W2" s="46" t="str">
         <f t="shared" ref="W2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
       <c r="X2" s="63" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Y2" s="64" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Z2" s="44" t="s">
         <v>174</v>
@@ -2451,12 +2426,12 @@
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="40">
         <v>3</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>14</v>
@@ -2486,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="42" t="str">
-        <f t="shared" ref="L2:N21" si="5">CONCATENATE("", C3)</f>
+        <f t="shared" ref="L3:N21" si="5">CONCATENATE("", C3)</f>
         <v>SomaSUS</v>
       </c>
       <c r="M3" s="42" t="str">
@@ -2498,7 +2473,7 @@
         <v>SUS.Ambientes</v>
       </c>
       <c r="O3" s="42" t="str">
-        <f t="shared" ref="O2:O22" si="6">F3</f>
+        <f t="shared" ref="O3:O22" si="6">F3</f>
         <v>SUS.Area</v>
       </c>
       <c r="P3" s="42" t="s">
@@ -2511,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="42" t="str">
-        <f t="shared" ref="S2:U21" si="7">SUBSTITUTE(D3, "_", " ")</f>
+        <f t="shared" ref="S3:U21" si="7">SUBSTITUTE(D3, "_", " ")</f>
         <v>SUS.Ocupação</v>
       </c>
       <c r="T3" s="42" t="str">
@@ -2523,32 +2498,32 @@
         <v>SUS.Area</v>
       </c>
       <c r="V3" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W3" s="46" t="str">
-        <f t="shared" ref="W2:W22" si="8">CONCATENATE("Key-SUS-",A3)</f>
+        <f t="shared" ref="W3:W22" si="8">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
       <c r="X3" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y3" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z3" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="Z3" s="44" t="s">
-        <v>176</v>
-      </c>
       <c r="AA3" s="43" t="str">
-        <f t="shared" ref="AA2:AA22" si="9">_xlfn.TRANSLATE(P3,"pt","en")</f>
+        <f t="shared" ref="AA3:AA22" si="9">_xlfn.TRANSLATE(P3,"pt","en")</f>
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="40">
         <v>4</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>14</v>
@@ -2615,32 +2590,32 @@
         <v>SUS.Box</v>
       </c>
       <c r="V4" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W4" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-4</v>
       </c>
       <c r="X4" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y4" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z4" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z4" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA4" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40">
         <v>5</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>14</v>
@@ -2707,32 +2682,32 @@
         <v>SUS.Consultório</v>
       </c>
       <c r="V5" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W5" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-5</v>
       </c>
       <c r="X5" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y5" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z5" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z5" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA5" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="40">
         <v>6</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>14</v>
@@ -2799,32 +2774,32 @@
         <v>SUS.Enfermaria</v>
       </c>
       <c r="V6" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W6" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-6</v>
       </c>
       <c r="X6" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y6" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z6" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z6" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA6" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="40">
         <v>7</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C7" s="56" t="s">
         <v>14</v>
@@ -2891,32 +2866,32 @@
         <v>SUS.Laboratório</v>
       </c>
       <c r="V7" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W7" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-7</v>
       </c>
       <c r="X7" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y7" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z7" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z7" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA7" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40">
         <v>8</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>14</v>
@@ -2983,32 +2958,32 @@
         <v>SUS.Piscina</v>
       </c>
       <c r="V8" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W8" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-8</v>
       </c>
       <c r="X8" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y8" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z8" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z8" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA8" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="40">
         <v>9</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C9" s="56" t="s">
         <v>14</v>
@@ -3075,32 +3050,32 @@
         <v>SUS.Posto</v>
       </c>
       <c r="V9" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W9" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-9</v>
       </c>
       <c r="X9" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y9" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z9" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z9" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA9" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="40">
         <v>10</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C10" s="56" t="s">
         <v>14</v>
@@ -3167,32 +3142,32 @@
         <v>SUS.Quarto</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W10" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-10</v>
       </c>
       <c r="X10" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y10" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z10" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z10" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA10" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40">
         <v>11</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11" s="56" t="s">
         <v>14</v>
@@ -3259,32 +3234,32 @@
         <v>SUS.Sala</v>
       </c>
       <c r="V11" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W11" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-11</v>
       </c>
       <c r="X11" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y11" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z11" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="Z11" s="44" t="s">
-        <v>176</v>
       </c>
       <c r="AA11" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="40">
         <v>12</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C12" s="56" t="s">
         <v>14</v>
@@ -3351,32 +3326,32 @@
         <v>SUS.Zoneamento</v>
       </c>
       <c r="V12" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W12" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-12</v>
       </c>
       <c r="X12" s="43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="Z12" s="44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA12" s="43" t="str">
         <f t="shared" si="9"/>
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="40">
         <v>13</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>14</v>
@@ -3443,32 +3418,32 @@
         <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="V13" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W13" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-13</v>
       </c>
       <c r="X13" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y13" s="43" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z13" s="44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA13" s="43" t="str">
         <f t="shared" si="9"/>
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="40">
         <v>14</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C14" s="56" t="s">
         <v>14</v>
@@ -3535,32 +3510,32 @@
         <v>SUS.Setor</v>
       </c>
       <c r="V14" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W14" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-14</v>
       </c>
       <c r="X14" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y14" s="43" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z14" s="44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA14" s="43" t="str">
         <f t="shared" si="9"/>
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="40">
         <v>15</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C15" s="56" t="s">
         <v>14</v>
@@ -3627,32 +3602,32 @@
         <v>SUS.Robot</v>
       </c>
       <c r="V15" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W15" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-15</v>
       </c>
       <c r="X15" s="43" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Y15" s="43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA15" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40">
         <v>16</v>
       </c>
       <c r="B16" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C16" s="56" t="s">
         <v>14</v>
@@ -3719,32 +3694,32 @@
         <v>SUS.Equipamento</v>
       </c>
       <c r="V16" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W16" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-16</v>
       </c>
       <c r="X16" s="43" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Y16" s="43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z16" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA16" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="40">
         <v>17</v>
       </c>
       <c r="B17" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C17" s="56" t="s">
         <v>14</v>
@@ -3811,32 +3786,32 @@
         <v>SUS.Dispositivo</v>
       </c>
       <c r="V17" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W17" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-17</v>
       </c>
       <c r="X17" s="43" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Y17" s="43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z17" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA17" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="40">
         <v>18</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C18" s="56" t="s">
         <v>14</v>
@@ -3903,32 +3878,32 @@
         <v>SUS.Instrumento</v>
       </c>
       <c r="V18" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W18" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-18</v>
       </c>
       <c r="X18" s="43" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Y18" s="43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z18" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA18" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="40">
         <v>19</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C19" s="56" t="s">
         <v>14</v>
@@ -3995,32 +3970,32 @@
         <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="V19" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W19" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-19</v>
       </c>
       <c r="X19" s="43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y19" s="43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z19" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA19" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="40">
         <v>20</v>
       </c>
       <c r="B20" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C20" s="56" t="s">
         <v>14</v>
@@ -4087,32 +4062,32 @@
         <v>SUS.Mobília</v>
       </c>
       <c r="V20" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W20" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-20</v>
       </c>
       <c r="X20" s="43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y20" s="43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z20" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA20" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="40">
         <v>21</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C21" s="56" t="s">
         <v>14</v>
@@ -4179,32 +4154,32 @@
         <v>SUS.Roupa</v>
       </c>
       <c r="V21" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W21" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-21</v>
       </c>
       <c r="X21" s="43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z21" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA21" s="43" t="str">
         <f t="shared" si="9"/>
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="40">
         <v>22</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C22" s="56" t="s">
         <v>14</v>
@@ -4271,20 +4246,20 @@
         <v>SUS.Alimentação</v>
       </c>
       <c r="V22" s="43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W22" s="46" t="str">
         <f t="shared" si="8"/>
         <v>Key-SUS-22</v>
       </c>
       <c r="X22" s="43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y22" s="43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z22" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA22" s="43" t="str">
         <f t="shared" si="9"/>
@@ -4293,57 +4268,47 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A3:B22">
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B22">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:F22 L3:Q22">
-    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
+  <conditionalFormatting sqref="D2:F2 L2:Q22">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="21" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X3:XFD22">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+  <conditionalFormatting sqref="D3:F22">
+    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S3:V22">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F18">
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:F22">
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X3:XFD22">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:XFD2 S2:V22">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F2 L2:Q2">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:XFD2 S2:V2">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4359,19 +4324,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
@@ -4436,7 +4401,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -4504,7 +4469,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4520,14 +4485,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -4538,7 +4503,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -4551,7 +4516,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4563,26 +4528,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.84375" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.69140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3828125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.69140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.53515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.84375" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -4629,7 +4594,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -4643,31 +4608,31 @@
         <v>83</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F2" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H2" s="37" t="s">
         <v>170</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J2" s="37" t="s">
         <v>171</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N2" s="37" t="s">
         <v>1</v>
@@ -4676,7 +4641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -4690,31 +4655,31 @@
         <v>83</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F3" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H3" s="37" t="s">
         <v>170</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J3" s="37" t="s">
         <v>171</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N3" s="37" t="s">
         <v>1</v>
@@ -4723,7 +4688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -4737,31 +4702,31 @@
         <v>83</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F4" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H4" s="37" t="s">
         <v>170</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J4" s="37" t="s">
         <v>171</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N4" s="37" t="s">
         <v>1</v>
@@ -4770,7 +4735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -4784,31 +4749,31 @@
         <v>83</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F5" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H5" s="37" t="s">
         <v>170</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J5" s="37" t="s">
         <v>171</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N5" s="37" t="s">
         <v>1</v>
@@ -4819,37 +4784,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B7EFD4-41C5-4454-94C8-AA6B77AF3092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E8B9DE-9EED-46FE-BBDB-03151E4B1C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="248">
   <si>
     <t>Key</t>
   </si>
@@ -376,9 +376,6 @@
     <t>CategoriaRvt</t>
   </si>
   <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -625,9 +622,6 @@
     <t>[ IfcFurniture ]</t>
   </si>
   <si>
-    <t>Hospitalar</t>
-  </si>
-  <si>
     <t>"[ 5I.10.28 ]"</t>
   </si>
   <si>
@@ -755,6 +749,81 @@
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>It refers to an environment that is not totally cloistered.</t>
+  </si>
+  <si>
+    <t>It refers to a closed and small environment, usually to serve patients.</t>
+  </si>
+  <si>
+    <t>It refers to a doctor's office-type environment.</t>
+  </si>
+  <si>
+    <t>It refers to an environment equipped to fulfill ward functions.</t>
+  </si>
+  <si>
+    <t>It refers to an environment equipped to perform laboratory functions.</t>
+  </si>
+  <si>
+    <t>It refers to a closed or open environment for medical treatment pools.</t>
+  </si>
+  <si>
+    <t>It refers to a nursing station associated with an infirmary.</t>
+  </si>
+  <si>
+    <t>It refers to a hospitalization room.</t>
+  </si>
+  <si>
+    <t>It refers to a room to function as administrative or technical service.</t>
+  </si>
+  <si>
+    <t>It refers to a defined zoning.</t>
+  </si>
+  <si>
+    <t>They are the functional units of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>They are the Sectors of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</t>
+  </si>
+  <si>
+    <t>Medical devices used in hospitals of the Brazilian Unified Health System.</t>
+  </si>
+  <si>
+    <t>Medical instrument used in hospitals of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>Medical furniture used in hospitals of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>Bed robe used in hospitals of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>Elements for feeding used in hospitals of the Unified Health System of Brazil.</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Parâmetro RVT</t>
+  </si>
+  <si>
+    <t>Hospitalar Público</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1303,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -1305,6 +1374,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1753,14 +1830,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3828125" customWidth="1"/>
-    <col min="2" max="2" width="48.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -1768,10 +1845,10 @@
         <v>48</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
@@ -1779,10 +1856,10 @@
         <v>96</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -1790,10 +1867,10 @@
         <v>77</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -1801,10 +1878,10 @@
         <v>25</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -1813,10 +1890,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -1825,10 +1902,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -1836,21 +1913,21 @@
         <v>55</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -1858,10 +1935,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -1869,10 +1946,10 @@
         <v>60</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -1880,10 +1957,10 @@
         <v>60</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -1891,10 +1968,10 @@
         <v>60</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -1902,10 +1979,10 @@
         <v>82</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -1913,10 +1990,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -1924,10 +2001,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -1935,10 +2012,10 @@
         <v>60</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -1946,22 +2023,22 @@
         <v>68</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46249.44650150463</v>
+        <v>46253.691729166669</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -1969,10 +2046,10 @@
         <v>60</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -1980,56 +2057,56 @@
         <v>60</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>168</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>169</v>
       </c>
       <c r="B22" s="17" t="str">
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
@@ -2037,173 +2114,173 @@
         <v>74</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="50" t="s">
+      <c r="B28" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="14" t="s">
+      <c r="C28" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B29" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="14" t="s">
+      <c r="C29" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B30" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
+      <c r="C30" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B31" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="s">
+      <c r="C31" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B32" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="s">
+      <c r="C32" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B33" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="C32" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
+      <c r="C33" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B34" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="C33" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
+      <c r="C34" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B35" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="C34" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
+      <c r="C35" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B35" s="52" t="s">
+      <c r="B36" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="C35" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="s">
+      <c r="C36" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="B37" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
+      <c r="C37" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="52" t="s">
+      <c r="B38" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="16" t="s">
+      <c r="C38" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B39" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
+      <c r="C39" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B40" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="C39" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="49" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="B40" s="54" t="s">
-        <v>217</v>
-      </c>
       <c r="C40" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2222,36 +2299,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AC22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.53515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="35.23046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="25.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.07421875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="34.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.84375" style="1"/>
+    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="36" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="36.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2303,52 +2382,58 @@
       <c r="Q1" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="S1" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="28" t="s">
+      <c r="T1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="U1" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="V1" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="28" t="s">
+      <c r="W1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="45" t="s">
+      <c r="X1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="28" t="s">
+      <c r="Y1" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="Z1" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA1" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB1" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC1" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA1" s="39" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="40">
         <v>2</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F2" s="58" t="s">
         <v>95</v>
@@ -2385,62 +2470,67 @@
         <v>SUS.Volume</v>
       </c>
       <c r="P2" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q2" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="Q2" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="R2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="42" t="str">
-        <f t="shared" ref="S2:U2" si="2">SUBSTITUTE(D2, "_", " ")</f>
+      <c r="R2" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="S2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="42" t="str">
+        <f t="shared" ref="T2:V2" si="2">SUBSTITUTE(D2, "_", " ")</f>
         <v>SUS.Caderno</v>
       </c>
-      <c r="T2" s="42" t="str">
+      <c r="U2" s="42" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="U2" s="42" t="str">
+      <c r="V2" s="42" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Volume</v>
       </c>
-      <c r="V2" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W2" s="46" t="str">
-        <f t="shared" ref="W2" si="3">CONCATENATE("Key-SUS-",A2)</f>
+      <c r="W2" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X2" s="46" t="str">
+        <f t="shared" ref="X2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="X2" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="Y2" s="64" t="s">
-        <v>224</v>
+      <c r="Y2" s="63" t="s">
+        <v>221</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA2" s="43" t="str">
-        <f t="shared" ref="AA2" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA2" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB2" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC2" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40">
         <v>3</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="59" t="s">
         <v>129</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>130</v>
       </c>
       <c r="F3" s="60" t="s">
         <v>86</v>
@@ -2461,541 +2551,571 @@
         <v>1</v>
       </c>
       <c r="L3" s="42" t="str">
-        <f t="shared" ref="L3:N21" si="5">CONCATENATE("", C3)</f>
+        <f t="shared" ref="L3:N21" si="4">CONCATENATE("", C3)</f>
         <v>SomaSUS</v>
       </c>
       <c r="M3" s="42" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
       <c r="N3" s="42" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
       <c r="O3" s="42" t="str">
-        <f t="shared" ref="O3:O22" si="6">F3</f>
+        <f t="shared" ref="O3:O22" si="5">F3</f>
         <v>SUS.Area</v>
       </c>
       <c r="P3" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="Q3" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="R3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="42" t="str">
-        <f t="shared" ref="S3:U21" si="7">SUBSTITUTE(D3, "_", " ")</f>
+      <c r="R3" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="S3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="42" t="str">
+        <f t="shared" ref="T3:V21" si="6">SUBSTITUTE(D3, "_", " ")</f>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="T3" s="42" t="str">
-        <f t="shared" si="7"/>
+      <c r="U3" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="U3" s="42" t="str">
-        <f t="shared" si="7"/>
+      <c r="V3" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Area</v>
       </c>
-      <c r="V3" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W3" s="46" t="str">
-        <f t="shared" ref="W3:W22" si="8">CONCATENATE("Key-SUS-",A3)</f>
+      <c r="W3" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X3" s="46" t="str">
+        <f t="shared" ref="X3:X22" si="7">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
-      <c r="X3" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y3" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z3" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA3" s="43" t="str">
-        <f t="shared" ref="AA3:AA22" si="9">_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>It refers to an environment that is not totally cloistered.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA3" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB3" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC3" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40">
         <v>4</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F4" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M4" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N4" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O4" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Box</v>
+      </c>
+      <c r="P4" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M4" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q4" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="R4" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="S4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N4" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U4" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O4" s="42" t="str">
+      <c r="V4" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Box</v>
       </c>
-      <c r="P4" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q4" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="R4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="42" t="str">
+      <c r="W4" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X4" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T4" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U4" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Box</v>
-      </c>
-      <c r="V4" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W4" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-4</v>
       </c>
-      <c r="X4" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y4" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA4" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a closed and small environment, usually to serve patients.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA4" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB4" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC4" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="40">
         <v>5</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F5" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M5" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N5" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O5" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Consultório</v>
+      </c>
+      <c r="P5" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M5" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q5" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="R5" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="S5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N5" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U5" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O5" s="42" t="str">
+      <c r="V5" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="P5" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q5" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="R5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="42" t="str">
+      <c r="W5" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X5" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T5" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U5" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Consultório</v>
-      </c>
-      <c r="V5" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W5" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-5</v>
       </c>
-      <c r="X5" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y5" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z5" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA5" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a doctor's office-type environment.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA5" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB5" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC5" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="40">
         <v>6</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F6" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M6" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N6" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O6" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Enfermaria</v>
+      </c>
+      <c r="P6" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M6" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q6" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="R6" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="S6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N6" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U6" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O6" s="42" t="str">
+      <c r="V6" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="P6" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q6" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="R6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="42" t="str">
+      <c r="W6" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X6" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T6" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U6" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Enfermaria</v>
-      </c>
-      <c r="V6" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W6" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-6</v>
       </c>
-      <c r="X6" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y6" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z6" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA6" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to an environment equipped to fulfill ward functions.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA6" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB6" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC6" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="40">
         <v>7</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C7" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E7" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F7" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M7" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N7" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O7" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Laboratório</v>
+      </c>
+      <c r="P7" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M7" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q7" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="R7" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="S7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N7" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U7" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O7" s="42" t="str">
+      <c r="V7" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="P7" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="R7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="42" t="str">
+      <c r="W7" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X7" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T7" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U7" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Laboratório</v>
-      </c>
-      <c r="V7" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W7" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-7</v>
       </c>
-      <c r="X7" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y7" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z7" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA7" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to an environment equipped to perform laboratory functions.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA7" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB7" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC7" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="40">
         <v>8</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F8" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M8" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N8" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O8" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Piscina</v>
+      </c>
+      <c r="P8" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M8" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q8" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="R8" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="S8" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N8" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U8" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O8" s="42" t="str">
+      <c r="V8" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="P8" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q8" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="42" t="str">
+      <c r="W8" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X8" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T8" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U8" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Piscina</v>
-      </c>
-      <c r="V8" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W8" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-8</v>
       </c>
-      <c r="X8" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y8" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z8" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA8" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a closed or open environment for medical treatment pools.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA8" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB8" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC8" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="40">
         <v>9</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C9" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F9" s="60" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G9" s="41" t="s">
         <v>1</v>
@@ -3013,262 +3133,277 @@
         <v>1</v>
       </c>
       <c r="L9" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M9" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N9" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O9" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M9" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Posto</v>
+      </c>
+      <c r="P9" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q9" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="S9" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N9" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U9" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O9" s="42" t="str">
+      <c r="V9" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="P9" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q9" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="R9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="42" t="str">
+      <c r="W9" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X9" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T9" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U9" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Posto</v>
-      </c>
-      <c r="V9" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W9" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-9</v>
       </c>
-      <c r="X9" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y9" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z9" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA9" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a nursing station associated with an infirmary.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA9" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB9" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC9" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="40">
         <v>10</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C10" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F10" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M10" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N10" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O10" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Quarto</v>
+      </c>
+      <c r="P10" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="G10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M10" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q10" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="S10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N10" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U10" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O10" s="42" t="str">
+      <c r="V10" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="P10" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="R10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="42" t="str">
+      <c r="W10" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X10" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T10" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U10" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Quarto</v>
-      </c>
-      <c r="V10" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W10" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-10</v>
       </c>
-      <c r="X10" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y10" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA10" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a hospitalization room.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA10" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB10" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC10" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="40">
         <v>11</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C11" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="59" t="s">
-        <v>130</v>
-      </c>
       <c r="F11" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M11" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N11" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ambientes</v>
+      </c>
+      <c r="O11" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Sala</v>
+      </c>
+      <c r="P11" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M11" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q11" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="S11" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N11" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U11" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O11" s="42" t="str">
+      <c r="V11" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="P11" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q11" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="R11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="42" t="str">
+      <c r="W11" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X11" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T11" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Ambientes</v>
-      </c>
-      <c r="U11" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Sala</v>
-      </c>
-      <c r="V11" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W11" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-11</v>
       </c>
-      <c r="X11" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y11" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z11" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA11" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a room to function as administrative or technical service.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA11" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB11" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC11" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="40">
         <v>12</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C12" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F12" s="62" t="s">
         <v>89</v>
@@ -3289,78 +3424,83 @@
         <v>1</v>
       </c>
       <c r="L12" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M12" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N12" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Funcional</v>
+      </c>
+      <c r="O12" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M12" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Zoneamento</v>
+      </c>
+      <c r="P12" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q12" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="R12" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="S12" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N12" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U12" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O12" s="42" t="str">
+      <c r="V12" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="P12" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q12" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="R12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="42" t="str">
+      <c r="W12" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X12" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T12" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Funcional</v>
-      </c>
-      <c r="U12" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Zoneamento</v>
-      </c>
-      <c r="V12" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W12" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-12</v>
       </c>
-      <c r="X12" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y12" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z12" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA12" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>It refers to a defined zoning.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA12" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB12" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC12" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="40">
         <v>13</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13" s="59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F13" s="62" t="s">
         <v>87</v>
@@ -3381,78 +3521,83 @@
         <v>1</v>
       </c>
       <c r="L13" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M13" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N13" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Funcional</v>
+      </c>
+      <c r="O13" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M13" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Unidade.Funcional</v>
+      </c>
+      <c r="P13" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q13" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="R13" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="S13" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N13" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U13" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O13" s="42" t="str">
+      <c r="V13" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="P13" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q13" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="R13" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="42" t="str">
+      <c r="W13" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X13" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T13" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Funcional</v>
-      </c>
-      <c r="U13" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Unidade.Funcional</v>
-      </c>
-      <c r="V13" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W13" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-13</v>
       </c>
-      <c r="X13" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y13" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z13" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA13" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>They are the functional units of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA13" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB13" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC13" s="44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="40">
         <v>14</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C14" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" s="62" t="s">
         <v>88</v>
@@ -3473,170 +3618,180 @@
         <v>1</v>
       </c>
       <c r="L14" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M14" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Ocupação</v>
+      </c>
+      <c r="N14" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Funcional</v>
+      </c>
+      <c r="O14" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M14" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Setor</v>
+      </c>
+      <c r="P14" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q14" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="R14" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="S14" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N14" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U14" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O14" s="42" t="str">
+      <c r="V14" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="P14" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q14" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="R14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="42" t="str">
+      <c r="W14" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X14" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Ocupação</v>
-      </c>
-      <c r="T14" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Funcional</v>
-      </c>
-      <c r="U14" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Setor</v>
-      </c>
-      <c r="V14" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W14" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-14</v>
       </c>
-      <c r="X14" s="43" t="s">
-        <v>220</v>
-      </c>
       <c r="Y14" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z14" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA14" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>They are the Sectors of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+      <c r="AA14" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB14" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC14" s="44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="40">
         <v>15</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C15" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F15" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M15" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N15" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Equipamentos</v>
+      </c>
+      <c r="O15" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Robot</v>
+      </c>
+      <c r="P15" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M15" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q15" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="R15" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="S15" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N15" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U15" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O15" s="42" t="str">
+      <c r="V15" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="P15" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q15" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="R15" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="42" t="str">
+      <c r="W15" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X15" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T15" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U15" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Robot</v>
-      </c>
-      <c r="V15" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W15" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-15</v>
       </c>
-      <c r="X15" s="43" t="s">
-        <v>222</v>
-      </c>
       <c r="Y15" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z15" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA15" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB15" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC15" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="Z15" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA15" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="40">
         <v>16</v>
       </c>
       <c r="B16" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C16" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>90</v>
@@ -3657,78 +3812,83 @@
         <v>1</v>
       </c>
       <c r="L16" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M16" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N16" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Equipamentos</v>
+      </c>
+      <c r="O16" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M16" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Equipamento</v>
+      </c>
+      <c r="P16" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q16" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="R16" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="S16" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N16" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U16" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O16" s="42" t="str">
+      <c r="V16" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="P16" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q16" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="R16" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="42" t="str">
+      <c r="W16" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X16" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T16" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U16" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamento</v>
-      </c>
-      <c r="V16" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W16" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-16</v>
       </c>
-      <c r="X16" s="43" t="s">
-        <v>222</v>
-      </c>
       <c r="Y16" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z16" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA16" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB16" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC16" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="Z16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA16" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="40">
         <v>17</v>
       </c>
       <c r="B17" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C17" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F17" s="62" t="s">
         <v>91</v>
@@ -3749,173 +3909,183 @@
         <v>1</v>
       </c>
       <c r="L17" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M17" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N17" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Equipamentos</v>
+      </c>
+      <c r="O17" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M17" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Dispositivo</v>
+      </c>
+      <c r="P17" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q17" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="R17" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="S17" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N17" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U17" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O17" s="42" t="str">
+      <c r="V17" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="P17" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q17" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="R17" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="42" t="str">
+      <c r="W17" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X17" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T17" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U17" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Dispositivo</v>
-      </c>
-      <c r="V17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W17" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-17</v>
       </c>
-      <c r="X17" s="43" t="s">
-        <v>222</v>
-      </c>
       <c r="Y17" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z17" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA17" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB17" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC17" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="Z17" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA17" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="40">
         <v>18</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C18" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F18" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M18" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N18" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Equipamentos</v>
+      </c>
+      <c r="O18" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Instrumento</v>
+      </c>
+      <c r="P18" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="G18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="42" t="str">
-        <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M18" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q18" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="R18" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="S18" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N18" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U18" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O18" s="42" t="str">
+      <c r="V18" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="P18" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q18" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="R18" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="42" t="str">
+      <c r="W18" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X18" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T18" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U18" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Instrumento</v>
-      </c>
-      <c r="V18" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W18" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-18</v>
       </c>
-      <c r="X18" s="43" t="s">
-        <v>222</v>
-      </c>
       <c r="Y18" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z18" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA18" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB18" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC18" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="Z18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA18" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>19</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C19" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E19" s="59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F19" s="62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19" s="41" t="s">
         <v>1</v>
@@ -3933,78 +4103,83 @@
         <v>1</v>
       </c>
       <c r="L19" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M19" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N19" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Equipamentos</v>
+      </c>
+      <c r="O19" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M19" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Mobília.de.Saúde</v>
+      </c>
+      <c r="P19" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q19" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="R19" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="S19" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N19" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U19" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O19" s="42" t="str">
+      <c r="V19" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="P19" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q19" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="R19" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="42" t="str">
+      <c r="W19" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X19" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T19" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Equipamentos</v>
-      </c>
-      <c r="U19" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Mobília.de.Saúde</v>
-      </c>
-      <c r="V19" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W19" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-19</v>
       </c>
-      <c r="X19" s="43" t="s">
+      <c r="Y19" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z19" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA19" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="Y19" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z19" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA19" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB19" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC19" s="44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>20</v>
       </c>
       <c r="B20" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C20" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="62" t="s">
         <v>92</v>
@@ -4025,82 +4200,87 @@
         <v>1</v>
       </c>
       <c r="L20" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M20" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N20" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Hotelaria</v>
+      </c>
+      <c r="O20" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M20" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Mobília</v>
+      </c>
+      <c r="P20" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q20" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="R20" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="S20" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N20" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U20" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O20" s="42" t="str">
+      <c r="V20" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="P20" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q20" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="R20" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="42" t="str">
+      <c r="W20" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X20" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T20" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="U20" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Mobília</v>
-      </c>
-      <c r="V20" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W20" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-20</v>
       </c>
-      <c r="X20" s="43" t="s">
+      <c r="Y20" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z20" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA20" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="Y20" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA20" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB20" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC20" s="44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>21</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C21" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E21" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="F21" s="62" t="s">
-        <v>159</v>
-      </c>
       <c r="G21" s="41" t="s">
         <v>1</v>
       </c>
@@ -4117,205 +4297,220 @@
         <v>1</v>
       </c>
       <c r="L21" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M21" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N21" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>SUS.Hotelaria</v>
+      </c>
+      <c r="O21" s="42" t="str">
         <f t="shared" si="5"/>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M21" s="42" t="str">
-        <f t="shared" si="5"/>
+        <v>SUS.Roupa</v>
+      </c>
+      <c r="P21" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q21" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="R21" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="S21" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N21" s="42" t="str">
-        <f t="shared" si="5"/>
+      <c r="U21" s="42" t="str">
+        <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O21" s="42" t="str">
+      <c r="V21" s="42" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="P21" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q21" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="R21" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="42" t="str">
+      <c r="W21" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X21" s="46" t="str">
         <f t="shared" si="7"/>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T21" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="U21" s="42" t="str">
-        <f t="shared" si="7"/>
-        <v>SUS.Roupa</v>
-      </c>
-      <c r="V21" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W21" s="46" t="str">
-        <f t="shared" si="8"/>
         <v>Key-SUS-21</v>
       </c>
-      <c r="X21" s="43" t="s">
+      <c r="Y21" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z21" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA21" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="Y21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z21" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA21" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB21" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC21" s="44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>22</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C22" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F22" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="42" t="str">
+        <f t="shared" ref="L22:N22" si="8">CONCATENATE("", C22)</f>
+        <v>SomaSUS</v>
+      </c>
+      <c r="M22" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>SUS.Assistência.Médica</v>
+      </c>
+      <c r="N22" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>SUS.Hotelaria</v>
+      </c>
+      <c r="O22" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>SUS.Alimentação</v>
+      </c>
+      <c r="P22" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="G22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="42" t="str">
-        <f t="shared" ref="L22:N22" si="10">CONCATENATE("", C22)</f>
-        <v>SomaSUS</v>
-      </c>
-      <c r="M22" s="42" t="str">
-        <f t="shared" si="10"/>
+      <c r="Q22" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="R22" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="S22" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="42" t="str">
+        <f t="shared" ref="T22:V22" si="9">SUBSTITUTE(D22, "_", " ")</f>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N22" s="42" t="str">
-        <f t="shared" si="10"/>
+      <c r="U22" s="42" t="str">
+        <f t="shared" si="9"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O22" s="42" t="str">
-        <f t="shared" si="6"/>
+      <c r="V22" s="42" t="str">
+        <f t="shared" si="9"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="P22" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q22" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="R22" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" s="42" t="str">
-        <f t="shared" ref="S22:U22" si="11">SUBSTITUTE(D22, "_", " ")</f>
-        <v>SUS.Assistência.Médica</v>
-      </c>
-      <c r="T22" s="42" t="str">
-        <f t="shared" si="11"/>
-        <v>SUS.Hotelaria</v>
-      </c>
-      <c r="U22" s="42" t="str">
-        <f t="shared" si="11"/>
-        <v>SUS.Alimentação</v>
-      </c>
-      <c r="V22" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W22" s="46" t="str">
-        <f t="shared" si="8"/>
+      <c r="W22" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="X22" s="46" t="str">
+        <f t="shared" si="7"/>
         <v>Key-SUS-22</v>
       </c>
-      <c r="X22" s="43" t="s">
+      <c r="Y22" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z22" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA22" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="Y22" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z22" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA22" s="43" t="str">
-        <f t="shared" si="9"/>
-        <v>Elements for feeding used in hospitals of the Unified Health System of Brazil.</v>
+      <c r="AB22" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC22" s="44" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B22">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B22 Y3:Y22 AB2:XFD22 AA3:AA22 Z2:Z22">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X3:XFD22">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+  <conditionalFormatting sqref="T2:W22">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:XFD2 S2:V22">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="R3:R22">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
+  <conditionalFormatting sqref="R2">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W1 A23:XFD1048576 AB1:XFD1" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AD1:XFD1 AC23:XFD1048576 A23:P1048576 A1:P1 AA23:AA1048576 S23:Y1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4324,19 +4519,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.3828125" style="5"/>
+    <col min="22" max="16384" width="5.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
@@ -4401,7 +4596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -4485,14 +4680,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -4503,7 +4698,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -4528,26 +4723,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.69140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3828125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.69140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.53515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -4594,7 +4789,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -4608,31 +4803,31 @@
         <v>83</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F2" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H2" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="I2" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>171</v>
-      </c>
       <c r="K2" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N2" s="37" t="s">
         <v>1</v>
@@ -4641,7 +4836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -4655,31 +4850,31 @@
         <v>83</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F3" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H3" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="J3" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="I3" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>171</v>
-      </c>
       <c r="K3" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N3" s="37" t="s">
         <v>1</v>
@@ -4688,7 +4883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -4702,31 +4897,31 @@
         <v>83</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F4" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="J4" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>171</v>
-      </c>
       <c r="K4" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N4" s="37" t="s">
         <v>1</v>
@@ -4735,7 +4930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -4749,31 +4944,31 @@
         <v>83</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F5" s="37" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H5" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>171</v>
-      </c>
       <c r="K5" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N5" s="37" t="s">
         <v>1</v>

--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E8B9DE-9EED-46FE-BBDB-03151E4B1C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B13AD7-975C-4C86-B7B8-4FB009171F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="276">
   <si>
     <t>Key</t>
   </si>
@@ -589,12 +589,6 @@
     <t>Aviso</t>
   </si>
   <si>
-    <t>categoria.revit</t>
-  </si>
-  <si>
-    <t>classe.ifc</t>
-  </si>
-  <si>
     <t>Advertência</t>
   </si>
   <si>
@@ -643,9 +637,6 @@
     <t>"Volume 2 - Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
   </si>
   <si>
-    <t>"[ - ]"</t>
-  </si>
-  <si>
     <t>Fonte1</t>
   </si>
   <si>
@@ -824,13 +815,106 @@
   </si>
   <si>
     <t>Hospitalar Público</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>"Volumes"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -921,8 +1005,14 @@
       <name val="Arial Nova Cond"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1061,6 +1151,54 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1114,7 +1252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1211,9 +1349,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1230,9 +1365,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1297,13 +1429,98 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1365,6 +1582,66 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -1402,11 +1679,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1844,7 +2123,7 @@
       <c r="B1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="34" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1855,7 +2134,7 @@
       <c r="B2" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1866,7 +2145,7 @@
       <c r="B3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1877,7 +2156,7 @@
       <c r="B4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1889,7 +2168,7 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1901,7 +2180,7 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1912,7 +2191,7 @@
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1923,7 +2202,7 @@
       <c r="B8" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1934,7 +2213,7 @@
       <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1945,7 +2224,7 @@
       <c r="B10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1956,7 +2235,7 @@
       <c r="B11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1967,7 +2246,7 @@
       <c r="B12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1978,7 +2257,7 @@
       <c r="B13" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1989,7 +2268,7 @@
       <c r="B14" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2000,7 +2279,7 @@
       <c r="B15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2011,7 +2290,7 @@
       <c r="B16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2022,7 +2301,7 @@
       <c r="B17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2032,9 +2311,9 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46253.691729166669</v>
-      </c>
-      <c r="C18" s="36" t="s">
+        <v>46258.575961805553</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2045,7 +2324,7 @@
       <c r="B19" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2056,18 +2335,18 @@
       <c r="B20" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2079,19 +2358,19 @@
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="35" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B23" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="35" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2102,7 +2381,7 @@
       <c r="B24" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2113,7 +2392,7 @@
       <c r="B25" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="35" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2125,161 +2404,161 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="35" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="C27" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="C30" s="35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="B31" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="B30" s="52" t="s">
+    <row r="32" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="B32" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="B31" s="52" t="s">
+    <row r="33" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="B33" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B32" s="52" t="s">
+    <row r="34" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="B34" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C34" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="B33" s="48" t="s">
+    <row r="35" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="B35" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B34" s="48" t="s">
+    <row r="36" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="B36" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="B35" s="52" t="s">
+    <row r="37" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="14" t="s">
+      <c r="B37" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="B36" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="47" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B37" s="52" t="s">
-        <v>209</v>
-      </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="47" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="52" t="s">
         <v>210</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="C39" s="35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="47" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="C38" s="36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="14" t="s">
+      <c r="B40" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="B39" s="54" t="s">
-        <v>213</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="49" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="B40" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="35" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2299,7 +2578,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2349,19 +2628,19 @@
       <c r="F1" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="65" t="s">
         <v>35</v>
       </c>
       <c r="L1" s="28" t="s">
@@ -2382,7 +2661,7 @@
       <c r="Q1" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="38" t="s">
         <v>159</v>
       </c>
       <c r="S1" s="29" t="s">
@@ -2400,2117 +2679,2212 @@
       <c r="W1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="X1" s="45" t="s">
+      <c r="X1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="28" t="s">
         <v>97</v>
       </c>
       <c r="Z1" s="28" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AA1" s="28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AB1" s="28" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AC1" s="28" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40">
+      <c r="A2" s="39">
         <v>2</v>
       </c>
-      <c r="B2" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="56" t="s">
+      <c r="B2" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="57" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="42" t="str">
+      <c r="G2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="40" t="str">
         <f t="shared" ref="L2:N2" si="0">CONCATENATE("", C2)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M2" s="42" t="str">
+      <c r="M2" s="40" t="str">
         <f t="shared" si="0"/>
         <v>SUS.Caderno</v>
       </c>
-      <c r="N2" s="42" t="str">
+      <c r="N2" s="40" t="str">
         <f t="shared" si="0"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="O2" s="42" t="str">
+      <c r="O2" s="40" t="str">
         <f t="shared" ref="O2" si="1">F2</f>
         <v>SUS.Volume</v>
       </c>
-      <c r="P2" s="42" t="s">
+      <c r="P2" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="Q2" s="42" t="s">
+      <c r="Q2" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="R2" s="43" t="s">
-        <v>223</v>
-      </c>
-      <c r="S2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="42" t="str">
+      <c r="R2" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="S2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="40" t="str">
         <f t="shared" ref="T2:V2" si="2">SUBSTITUTE(D2, "_", " ")</f>
         <v>SUS.Caderno</v>
       </c>
-      <c r="U2" s="42" t="str">
+      <c r="U2" s="40" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="V2" s="42" t="str">
+      <c r="V2" s="40" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Volume</v>
       </c>
-      <c r="W2" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X2" s="46" t="str">
+      <c r="W2" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X2" s="44" t="str">
         <f t="shared" ref="X2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="Y2" s="63" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z2" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA2" s="64" t="s">
-        <v>222</v>
-      </c>
-      <c r="AB2" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC2" s="44" t="s">
-        <v>173</v>
+      <c r="Y2" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z2" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA2" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB2" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC2" s="42" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40">
+      <c r="A3" s="39">
         <v>3</v>
       </c>
-      <c r="B3" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" s="56" t="s">
+      <c r="B3" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="42" t="str">
+      <c r="G3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="40" t="str">
         <f t="shared" ref="L3:N21" si="4">CONCATENATE("", C3)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M3" s="42" t="str">
+      <c r="M3" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N3" s="42" t="str">
+      <c r="N3" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O3" s="42" t="str">
+      <c r="O3" s="40" t="str">
         <f t="shared" ref="O3:O22" si="5">F3</f>
         <v>SUS.Area</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="P3" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="Q3" s="42" t="s">
+      <c r="Q3" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="R3" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="S3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="42" t="str">
+      <c r="R3" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="S3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="40" t="str">
         <f t="shared" ref="T3:V21" si="6">SUBSTITUTE(D3, "_", " ")</f>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U3" s="42" t="str">
+      <c r="U3" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V3" s="42" t="str">
+      <c r="V3" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Area</v>
       </c>
-      <c r="W3" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X3" s="46" t="str">
-        <f t="shared" ref="X3:X22" si="7">CONCATENATE("Key-SUS-",A3)</f>
+      <c r="W3" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X3" s="44" t="str">
+        <f t="shared" ref="X3:X23" si="7">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
-      <c r="Y3" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z3" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA3" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB3" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC3" s="44" t="s">
-        <v>174</v>
+      <c r="Y3" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z3" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA3" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB3" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC3" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40">
+      <c r="A4" s="39">
         <v>4</v>
       </c>
-      <c r="B4" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="56" t="s">
+      <c r="B4" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="60" t="s">
+      <c r="F4" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="42" t="str">
+      <c r="G4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M4" s="42" t="str">
+      <c r="M4" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N4" s="42" t="str">
+      <c r="N4" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O4" s="42" t="str">
+      <c r="O4" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Box</v>
       </c>
-      <c r="P4" s="42" t="s">
+      <c r="P4" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="Q4" s="42" t="s">
+      <c r="Q4" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="43" t="s">
-        <v>225</v>
-      </c>
-      <c r="S4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="42" t="str">
+      <c r="R4" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="S4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U4" s="42" t="str">
+      <c r="U4" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V4" s="42" t="str">
+      <c r="V4" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Box</v>
       </c>
-      <c r="W4" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X4" s="46" t="str">
+      <c r="W4" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X4" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-4</v>
       </c>
-      <c r="Y4" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z4" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA4" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB4" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC4" s="44" t="s">
-        <v>174</v>
+      <c r="Y4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z4" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA4" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB4" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC4" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40">
+      <c r="A5" s="39">
         <v>5</v>
       </c>
-      <c r="B5" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="56" t="s">
+      <c r="B5" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="E5" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="42" t="str">
+      <c r="G5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M5" s="42" t="str">
+      <c r="M5" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N5" s="42" t="str">
+      <c r="N5" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O5" s="42" t="str">
+      <c r="O5" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="Q5" s="42" t="s">
+      <c r="Q5" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="R5" s="43" t="s">
-        <v>226</v>
-      </c>
-      <c r="S5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="42" t="str">
+      <c r="R5" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="S5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U5" s="42" t="str">
+      <c r="U5" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V5" s="42" t="str">
+      <c r="V5" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="W5" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X5" s="46" t="str">
+      <c r="W5" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X5" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-5</v>
       </c>
-      <c r="Y5" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z5" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA5" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB5" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC5" s="44" t="s">
-        <v>174</v>
+      <c r="Y5" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z5" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA5" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB5" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC5" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40">
+      <c r="A6" s="39">
         <v>6</v>
       </c>
-      <c r="B6" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="56" t="s">
+      <c r="B6" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="42" t="str">
+      <c r="G6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M6" s="42" t="str">
+      <c r="M6" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N6" s="42" t="str">
+      <c r="N6" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O6" s="42" t="str">
+      <c r="O6" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="Q6" s="42" t="s">
+      <c r="Q6" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="R6" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="S6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="42" t="str">
+      <c r="R6" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="S6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U6" s="42" t="str">
+      <c r="U6" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V6" s="42" t="str">
+      <c r="V6" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="W6" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X6" s="46" t="str">
+      <c r="W6" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X6" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-6</v>
       </c>
-      <c r="Y6" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z6" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA6" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB6" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC6" s="44" t="s">
-        <v>174</v>
+      <c r="Y6" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z6" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA6" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB6" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC6" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="40">
+      <c r="A7" s="39">
         <v>7</v>
       </c>
-      <c r="B7" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="56" t="s">
+      <c r="B7" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="F7" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="42" t="str">
+      <c r="G7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M7" s="42" t="str">
+      <c r="M7" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N7" s="42" t="str">
+      <c r="N7" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O7" s="42" t="str">
+      <c r="O7" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="P7" s="42" t="s">
+      <c r="P7" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="Q7" s="42" t="s">
+      <c r="Q7" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="R7" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="S7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="42" t="str">
+      <c r="R7" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="S7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U7" s="42" t="str">
+      <c r="U7" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V7" s="42" t="str">
+      <c r="V7" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="W7" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X7" s="46" t="str">
+      <c r="W7" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X7" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-7</v>
       </c>
-      <c r="Y7" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z7" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA7" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB7" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC7" s="44" t="s">
-        <v>174</v>
+      <c r="Y7" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z7" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA7" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB7" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC7" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="40">
+      <c r="A8" s="39">
         <v>8</v>
       </c>
-      <c r="B8" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="56" t="s">
+      <c r="B8" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="G8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="42" t="str">
+      <c r="G8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M8" s="42" t="str">
+      <c r="M8" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N8" s="42" t="str">
+      <c r="N8" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O8" s="42" t="str">
+      <c r="O8" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="P8" s="42" t="s">
+      <c r="P8" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="Q8" s="42" t="s">
+      <c r="Q8" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="R8" s="43" t="s">
-        <v>229</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="42" t="str">
+      <c r="R8" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U8" s="42" t="str">
+      <c r="U8" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V8" s="42" t="str">
+      <c r="V8" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="W8" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X8" s="46" t="str">
+      <c r="W8" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X8" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-8</v>
       </c>
-      <c r="Y8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z8" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA8" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB8" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC8" s="44" t="s">
-        <v>174</v>
+      <c r="Y8" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z8" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA8" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB8" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC8" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="40">
+      <c r="A9" s="39">
         <v>9</v>
       </c>
-      <c r="B9" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="56" t="s">
+      <c r="B9" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="F9" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="42" t="str">
+      <c r="G9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M9" s="42" t="str">
+      <c r="M9" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N9" s="42" t="str">
+      <c r="N9" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O9" s="42" t="str">
+      <c r="O9" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="P9" s="42" t="s">
+      <c r="P9" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="Q9" s="42" t="s">
+      <c r="Q9" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="R9" s="43" t="s">
-        <v>230</v>
-      </c>
-      <c r="S9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="42" t="str">
+      <c r="R9" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="S9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U9" s="42" t="str">
+      <c r="U9" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V9" s="42" t="str">
+      <c r="V9" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="W9" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X9" s="46" t="str">
+      <c r="W9" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X9" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-9</v>
       </c>
-      <c r="Y9" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z9" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA9" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB9" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC9" s="44" t="s">
-        <v>174</v>
+      <c r="Y9" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z9" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA9" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB9" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC9" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="40">
+      <c r="A10" s="39">
         <v>10</v>
       </c>
-      <c r="B10" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C10" s="56" t="s">
+      <c r="B10" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="60" t="s">
+      <c r="F10" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="G10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="42" t="str">
+      <c r="G10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M10" s="42" t="str">
+      <c r="M10" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N10" s="42" t="str">
+      <c r="N10" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O10" s="42" t="str">
+      <c r="O10" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="Q10" s="42" t="s">
+      <c r="Q10" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="R10" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="S10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="42" t="str">
+      <c r="R10" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="S10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U10" s="42" t="str">
+      <c r="U10" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V10" s="42" t="str">
+      <c r="V10" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="W10" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X10" s="46" t="str">
+      <c r="W10" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X10" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-10</v>
       </c>
-      <c r="Y10" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z10" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA10" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB10" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC10" s="44" t="s">
-        <v>174</v>
+      <c r="Y10" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z10" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA10" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB10" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC10" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40">
+      <c r="A11" s="39">
         <v>11</v>
       </c>
-      <c r="B11" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C11" s="56" t="s">
+      <c r="B11" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="G11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="42" t="str">
+      <c r="G11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M11" s="42" t="str">
+      <c r="M11" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N11" s="42" t="str">
+      <c r="N11" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O11" s="42" t="str">
+      <c r="O11" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="P11" s="42" t="s">
+      <c r="P11" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="Q11" s="42" t="s">
+      <c r="Q11" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="R11" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="S11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="42" t="str">
+      <c r="R11" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="S11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U11" s="42" t="str">
+      <c r="U11" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V11" s="42" t="str">
+      <c r="V11" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="W11" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X11" s="46" t="str">
+      <c r="W11" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X11" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-11</v>
       </c>
-      <c r="Y11" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z11" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA11" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB11" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC11" s="44" t="s">
-        <v>174</v>
+      <c r="Y11" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z11" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA11" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB11" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC11" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="40">
+      <c r="A12" s="39">
         <v>12</v>
       </c>
-      <c r="B12" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="56" t="s">
+      <c r="B12" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="E12" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="42" t="str">
+      <c r="G12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M12" s="42" t="str">
+      <c r="M12" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N12" s="42" t="str">
+      <c r="N12" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O12" s="42" t="str">
+      <c r="O12" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="P12" s="42" t="s">
+      <c r="P12" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="Q12" s="42" t="s">
+      <c r="Q12" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="R12" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="S12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="42" t="str">
+      <c r="R12" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="S12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U12" s="42" t="str">
+      <c r="U12" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V12" s="42" t="str">
+      <c r="V12" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="W12" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X12" s="46" t="str">
+      <c r="W12" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X12" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-12</v>
       </c>
-      <c r="Y12" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z12" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA12" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB12" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC12" s="44" t="s">
-        <v>174</v>
+      <c r="Y12" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z12" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA12" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB12" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC12" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="40">
+      <c r="A13" s="39">
         <v>13</v>
       </c>
-      <c r="B13" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="56" t="s">
+      <c r="B13" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="42" t="str">
+      <c r="G13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M13" s="42" t="str">
+      <c r="M13" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N13" s="42" t="str">
+      <c r="N13" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O13" s="42" t="str">
+      <c r="O13" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="P13" s="42" t="s">
+      <c r="P13" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="Q13" s="42" t="s">
+      <c r="Q13" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="R13" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="S13" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="42" t="str">
+      <c r="R13" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="S13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U13" s="42" t="str">
+      <c r="U13" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V13" s="42" t="str">
+      <c r="V13" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="W13" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X13" s="46" t="str">
+      <c r="W13" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X13" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-13</v>
       </c>
-      <c r="Y13" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z13" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA13" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB13" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC13" s="44" t="s">
-        <v>175</v>
+      <c r="Y13" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z13" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA13" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB13" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC13" s="42" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="40">
+      <c r="A14" s="39">
         <v>14</v>
       </c>
-      <c r="B14" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14" s="56" t="s">
+      <c r="B14" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="62" t="s">
+      <c r="F14" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="42" t="str">
+      <c r="G14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M14" s="42" t="str">
+      <c r="M14" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N14" s="42" t="str">
+      <c r="N14" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O14" s="42" t="str">
+      <c r="O14" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="P14" s="42" t="s">
+      <c r="P14" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="Q14" s="42" t="s">
+      <c r="Q14" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="R14" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="S14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="42" t="str">
+      <c r="R14" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="S14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U14" s="42" t="str">
+      <c r="U14" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V14" s="42" t="str">
+      <c r="V14" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="W14" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X14" s="46" t="str">
+      <c r="W14" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X14" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-14</v>
       </c>
-      <c r="Y14" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z14" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA14" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB14" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC14" s="44" t="s">
-        <v>175</v>
+      <c r="Y14" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z14" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA14" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB14" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC14" s="42" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="40">
+      <c r="A15" s="39">
         <v>15</v>
       </c>
-      <c r="B15" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C15" s="56" t="s">
+      <c r="B15" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="59" t="s">
+      <c r="E15" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="42" t="str">
+      <c r="G15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M15" s="42" t="str">
+      <c r="M15" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N15" s="42" t="str">
+      <c r="N15" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O15" s="42" t="str">
+      <c r="O15" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="P15" s="42" t="s">
+      <c r="P15" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="Q15" s="42" t="s">
+      <c r="Q15" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="R15" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="S15" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="42" t="str">
+      <c r="R15" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="S15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U15" s="42" t="str">
+      <c r="U15" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V15" s="42" t="str">
+      <c r="V15" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="W15" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X15" s="46" t="str">
+      <c r="W15" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X15" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-15</v>
       </c>
-      <c r="Y15" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z15" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA15" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB15" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC15" s="44" t="s">
-        <v>177</v>
+      <c r="Y15" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z15" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA15" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB15" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC15" s="42" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="40">
+      <c r="A16" s="39">
         <v>16</v>
       </c>
-      <c r="B16" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="56" t="s">
+      <c r="B16" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="F16" s="62" t="s">
+      <c r="F16" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="42" t="str">
+      <c r="G16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M16" s="42" t="str">
+      <c r="M16" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N16" s="42" t="str">
+      <c r="N16" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O16" s="42" t="str">
+      <c r="O16" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="P16" s="42" t="s">
+      <c r="P16" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="Q16" s="42" t="s">
+      <c r="Q16" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="R16" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="S16" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="42" t="str">
+      <c r="R16" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="S16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U16" s="42" t="str">
+      <c r="U16" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V16" s="42" t="str">
+      <c r="V16" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="W16" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X16" s="46" t="str">
+      <c r="W16" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X16" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-16</v>
       </c>
-      <c r="Y16" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z16" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA16" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB16" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC16" s="44" t="s">
-        <v>177</v>
+      <c r="Y16" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z16" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA16" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB16" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC16" s="42" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="40">
+      <c r="A17" s="39">
         <v>17</v>
       </c>
-      <c r="B17" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="56" t="s">
+      <c r="B17" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="59" t="s">
+      <c r="E17" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F17" s="60" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="42" t="str">
+      <c r="G17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M17" s="42" t="str">
+      <c r="M17" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N17" s="42" t="str">
+      <c r="N17" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O17" s="42" t="str">
+      <c r="O17" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="P17" s="42" t="s">
+      <c r="P17" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="Q17" s="42" t="s">
+      <c r="Q17" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="R17" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="S17" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="42" t="str">
+      <c r="R17" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="S17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U17" s="42" t="str">
+      <c r="U17" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V17" s="42" t="str">
+      <c r="V17" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="W17" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X17" s="46" t="str">
+      <c r="W17" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X17" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-17</v>
       </c>
-      <c r="Y17" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z17" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA17" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB17" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC17" s="44" t="s">
-        <v>177</v>
+      <c r="Y17" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z17" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA17" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB17" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC17" s="42" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="40">
+      <c r="A18" s="39">
         <v>18</v>
       </c>
-      <c r="B18" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="56" t="s">
+      <c r="B18" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="62" t="s">
+      <c r="F18" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="G18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="42" t="str">
+      <c r="G18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M18" s="42" t="str">
+      <c r="M18" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N18" s="42" t="str">
+      <c r="N18" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O18" s="42" t="str">
+      <c r="O18" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="P18" s="42" t="s">
+      <c r="P18" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="Q18" s="42" t="s">
+      <c r="Q18" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="R18" s="43" t="s">
-        <v>239</v>
-      </c>
-      <c r="S18" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="42" t="str">
+      <c r="R18" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="S18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U18" s="42" t="str">
+      <c r="U18" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V18" s="42" t="str">
+      <c r="V18" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="W18" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X18" s="46" t="str">
+      <c r="W18" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X18" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-18</v>
       </c>
-      <c r="Y18" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z18" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA18" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB18" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC18" s="44" t="s">
-        <v>177</v>
+      <c r="Y18" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z18" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA18" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB18" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC18" s="42" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40">
+      <c r="A19" s="39">
         <v>19</v>
       </c>
-      <c r="B19" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="56" t="s">
+      <c r="B19" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="42" t="str">
+      <c r="G19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M19" s="42" t="str">
+      <c r="M19" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N19" s="42" t="str">
+      <c r="N19" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O19" s="42" t="str">
+      <c r="O19" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="P19" s="42" t="s">
+      <c r="P19" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="Q19" s="42" t="s">
+      <c r="Q19" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="R19" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="S19" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="42" t="str">
+      <c r="R19" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="S19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U19" s="42" t="str">
+      <c r="U19" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V19" s="42" t="str">
+      <c r="V19" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="W19" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X19" s="46" t="str">
+      <c r="W19" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X19" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-19</v>
       </c>
-      <c r="Y19" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z19" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA19" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB19" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC19" s="44" t="s">
+      <c r="Y19" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z19" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA19" s="41" t="s">
         <v>177</v>
       </c>
+      <c r="AB19" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC19" s="42" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40">
+      <c r="A20" s="39">
         <v>20</v>
       </c>
-      <c r="B20" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="56" t="s">
+      <c r="B20" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="62" t="s">
+      <c r="F20" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="42" t="str">
+      <c r="G20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M20" s="42" t="str">
+      <c r="M20" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N20" s="42" t="str">
+      <c r="N20" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O20" s="42" t="str">
+      <c r="O20" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="P20" s="42" t="s">
+      <c r="P20" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="Q20" s="42" t="s">
+      <c r="Q20" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="R20" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="S20" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T20" s="42" t="str">
+      <c r="R20" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="S20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U20" s="42" t="str">
+      <c r="U20" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V20" s="42" t="str">
+      <c r="V20" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="W20" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X20" s="46" t="str">
+      <c r="W20" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X20" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-20</v>
       </c>
-      <c r="Y20" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z20" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA20" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB20" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC20" s="44" t="s">
+      <c r="Y20" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z20" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA20" s="41" t="s">
         <v>177</v>
       </c>
+      <c r="AB20" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC20" s="42" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40">
+      <c r="A21" s="39">
         <v>21</v>
       </c>
-      <c r="B21" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="56" t="s">
+      <c r="B21" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="62" t="s">
+      <c r="F21" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="G21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="42" t="str">
+      <c r="G21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M21" s="42" t="str">
+      <c r="M21" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N21" s="42" t="str">
+      <c r="N21" s="40" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O21" s="42" t="str">
+      <c r="O21" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="P21" s="42" t="s">
+      <c r="P21" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="Q21" s="42" t="s">
+      <c r="Q21" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="R21" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="S21" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="42" t="str">
+      <c r="R21" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="S21" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U21" s="42" t="str">
+      <c r="U21" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V21" s="42" t="str">
+      <c r="V21" s="40" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="W21" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X21" s="46" t="str">
+      <c r="W21" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X21" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-21</v>
       </c>
-      <c r="Y21" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z21" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA21" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB21" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC21" s="44" t="s">
+      <c r="Y21" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z21" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA21" s="41" t="s">
         <v>177</v>
       </c>
+      <c r="AB21" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC21" s="42" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40">
+      <c r="A22" s="39">
         <v>22</v>
       </c>
-      <c r="B22" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" s="56" t="s">
+      <c r="B22" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="42" t="str">
+      <c r="G22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="40" t="str">
         <f t="shared" ref="L22:N22" si="8">CONCATENATE("", C22)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M22" s="42" t="str">
+      <c r="M22" s="40" t="str">
         <f t="shared" si="8"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N22" s="42" t="str">
+      <c r="N22" s="40" t="str">
         <f t="shared" si="8"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O22" s="42" t="str">
+      <c r="O22" s="40" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="P22" s="42" t="s">
+      <c r="P22" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="Q22" s="42" t="s">
+      <c r="Q22" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="R22" s="43" t="s">
-        <v>242</v>
-      </c>
-      <c r="S22" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="42" t="str">
+      <c r="R22" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="S22" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="40" t="str">
         <f t="shared" ref="T22:V22" si="9">SUBSTITUTE(D22, "_", " ")</f>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U22" s="42" t="str">
+      <c r="U22" s="40" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V22" s="42" t="str">
+      <c r="V22" s="40" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="W22" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="X22" s="46" t="str">
+      <c r="W22" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X22" s="44" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-22</v>
       </c>
-      <c r="Y22" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z22" s="44" t="s">
+      <c r="Y22" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z22" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA22" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB22" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC22" s="42" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="39">
+        <v>23</v>
+      </c>
+      <c r="B23" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="AA22" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB22" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="AC22" s="44" t="s">
-        <v>177</v>
+      <c r="C23" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>247</v>
+      </c>
+      <c r="E23" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="G23" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="40" t="str">
+        <f t="shared" ref="L23:O23" si="10">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M23" s="40" t="str">
+        <f t="shared" si="10"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N23" s="40" t="str">
+        <f t="shared" si="10"/>
+        <v>Macros</v>
+      </c>
+      <c r="O23" s="40" t="str">
+        <f t="shared" si="10"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P23" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q23" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="R23" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="S23" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="41" t="str">
+        <f t="shared" ref="T23:V23" si="11">SUBSTITUTE(C23, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U23" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V23" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="W23" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X23" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-SUS-23</v>
+      </c>
+      <c r="Y23" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="63" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B22 Y3:Y22 AB2:XFD22 AA3:AA22 Z2:Z22">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B23">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:W22">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
+  <conditionalFormatting sqref="F23">
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R23">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R22">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+  <conditionalFormatting sqref="T2:W22 W23">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+  <conditionalFormatting sqref="Z2:Z22 AB2:XFD22 Y3:Y22 AA3:AA22">
+    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="S1:X1 AD1:XFD1 AC23:XFD1048576 A23:P1048576 A1:P1 AA23:AA1048576 S23:Y1048576" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AD1:XFD1 AC24:XFD1048576 A24:P1048576 A1:P1 AA24:AA1048576 S24:Y1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4664,7 +5038,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4711,7 +5085,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4722,27 +5096,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
     <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="33" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.42578125" style="22" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="33" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="3.7109375" style="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -4758,16 +5131,16 @@
       <c r="E1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="21" t="s">
         <v>48</v>
       </c>
       <c r="J1" s="20" t="s">
@@ -4782,14 +5155,38 @@
       <c r="M1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="73" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="S1" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="U1" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="V1" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="W1" s="73" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -4799,44 +5196,68 @@
       <c r="C2" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="36" t="s">
         <v>83</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="F2" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="H2" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>170</v>
+      <c r="I2" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="J2" s="36" t="s">
+        <v>179</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>1</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="N2" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -4846,44 +5267,68 @@
       <c r="C3" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="36" t="s">
         <v>83</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="F3" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="H3" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>170</v>
+      <c r="I3" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>179</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="L3" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="L3" s="36" t="s">
+        <v>1</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="N3" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="32" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="N3" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -4893,44 +5338,68 @@
       <c r="C4" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="36" t="s">
         <v>83</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="F4" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="H4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>170</v>
+      <c r="I4" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>179</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>1</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="32" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="N4" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -4940,76 +5409,494 @@
       <c r="C5" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="36" t="s">
         <v>83</v>
       </c>
       <c r="E5" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="J5" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="L5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="23">
+        <v>6</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="N5" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="32" t="s">
+      <c r="I6" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="70" t="str">
+        <f t="shared" ref="L6:L10" si="0">IF(M6="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="M6" s="71" t="s">
+        <v>258</v>
+      </c>
+      <c r="N6" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="23">
+        <v>7</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="69" t="s">
+        <v>261</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="M7" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="N7" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23">
+        <v>8</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="69" t="s">
+        <v>265</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="M8" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="N8" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="23">
+        <v>9</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="69" t="s">
+        <v>268</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="69" t="s">
+        <v>269</v>
+      </c>
+      <c r="J9" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="M9" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="N9" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="23">
+        <v>10</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="G10" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="69" t="s">
+        <v>273</v>
+      </c>
+      <c r="J10" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="M10" s="71" t="s">
+        <v>274</v>
+      </c>
+      <c r="N10" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="75" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B6:B10">
+    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="40" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1">
+    <cfRule type="cellIs" dxfId="15" priority="36" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1">
+    <cfRule type="cellIs" dxfId="14" priority="33" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:K10">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:M5 F1:I1 A1:E2 X1:XFD5 H2:I5 B3:E5 A3:A10 A11:M1048576 X11:XFD1048576">
+    <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1">
+    <cfRule type="cellIs" dxfId="11" priority="20" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:W1">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+  <conditionalFormatting sqref="P1">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+  <conditionalFormatting sqref="R1">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="T1">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="V1">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B13AD7-975C-4C86-B7B8-4FB009171F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123665FB-7682-454E-998E-DC0E9E4CC26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="275">
   <si>
     <t>Key</t>
   </si>
@@ -806,9 +806,6 @@
   </si>
   <si>
     <t>Classe IFC</t>
-  </si>
-  <si>
-    <t>[ - ]</t>
   </si>
   <si>
     <t>Parâmetro RVT</t>
@@ -1472,7 +1469,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="32">
     <dxf>
       <font>
         <b val="0"/>
@@ -1511,46 +1508,6 @@
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -2109,14 +2066,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.3828125" customWidth="1"/>
+    <col min="2" max="2" width="48.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -2127,7 +2084,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
@@ -2138,7 +2095,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -2149,7 +2106,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2160,7 +2117,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2172,7 +2129,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2184,7 +2141,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2195,7 +2152,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
@@ -2206,7 +2163,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2217,7 +2174,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2228,7 +2185,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2239,7 +2196,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2250,7 +2207,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2261,7 +2218,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2272,7 +2229,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2283,7 +2240,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2294,7 +2251,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2305,19 +2262,19 @@
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46258.575961805553</v>
+        <v>46264.577966550925</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
@@ -2328,7 +2285,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2339,7 +2296,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>169</v>
       </c>
@@ -2350,7 +2307,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>168</v>
       </c>
@@ -2362,7 +2319,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>170</v>
       </c>
@@ -2374,7 +2331,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
@@ -2385,7 +2342,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
@@ -2396,7 +2353,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>161</v>
       </c>
@@ -2408,7 +2365,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
         <v>185</v>
       </c>
@@ -2419,7 +2376,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
         <v>187</v>
       </c>
@@ -2430,7 +2387,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
         <v>189</v>
       </c>
@@ -2441,7 +2398,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
         <v>191</v>
       </c>
@@ -2452,7 +2409,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
         <v>193</v>
       </c>
@@ -2463,7 +2420,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
         <v>195</v>
       </c>
@@ -2474,7 +2431,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
         <v>197</v>
       </c>
@@ -2485,7 +2442,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
         <v>199</v>
       </c>
@@ -2496,7 +2453,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
         <v>201</v>
       </c>
@@ -2507,7 +2464,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
         <v>203</v>
       </c>
@@ -2518,7 +2475,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
         <v>205</v>
       </c>
@@ -2529,7 +2486,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16" t="s">
         <v>207</v>
       </c>
@@ -2540,7 +2497,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="47" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="47" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
@@ -2551,7 +2508,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="47" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" s="47" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
         <v>211</v>
       </c>
@@ -2579,37 +2536,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.84375" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.15234375" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.3828125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.85546875" style="1"/>
+    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2686,7 +2643,7 @@
         <v>97</v>
       </c>
       <c r="Z1" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AA1" s="28" t="s">
         <v>241</v>
@@ -2698,7 +2655,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="39">
         <v>2</v>
       </c>
@@ -2773,7 +2730,7 @@
         <v>SUS.Volume</v>
       </c>
       <c r="W2" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X2" s="44" t="str">
         <f t="shared" ref="X2" si="3">CONCATENATE("Key-SUS-",A2)</f>
@@ -2783,19 +2740,19 @@
         <v>218</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="62" t="s">
         <v>219</v>
       </c>
       <c r="AB2" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="42" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39">
         <v>3</v>
       </c>
@@ -2870,7 +2827,7 @@
         <v>SUS.Area</v>
       </c>
       <c r="W3" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X3" s="44" t="str">
         <f t="shared" ref="X3:X23" si="7">CONCATENATE("Key-SUS-",A3)</f>
@@ -2880,19 +2837,19 @@
         <v>215</v>
       </c>
       <c r="Z3" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB3" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="39">
         <v>4</v>
       </c>
@@ -2967,7 +2924,7 @@
         <v>SUS.Box</v>
       </c>
       <c r="W4" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X4" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2977,19 +2934,19 @@
         <v>215</v>
       </c>
       <c r="Z4" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB4" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="39">
         <v>5</v>
       </c>
@@ -3064,7 +3021,7 @@
         <v>SUS.Consultório</v>
       </c>
       <c r="W5" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X5" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3074,19 +3031,19 @@
         <v>215</v>
       </c>
       <c r="Z5" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB5" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="39">
         <v>6</v>
       </c>
@@ -3161,7 +3118,7 @@
         <v>SUS.Enfermaria</v>
       </c>
       <c r="W6" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X6" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3171,19 +3128,19 @@
         <v>215</v>
       </c>
       <c r="Z6" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB6" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="39">
         <v>7</v>
       </c>
@@ -3258,7 +3215,7 @@
         <v>SUS.Laboratório</v>
       </c>
       <c r="W7" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X7" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3268,19 +3225,19 @@
         <v>215</v>
       </c>
       <c r="Z7" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB7" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="39">
         <v>8</v>
       </c>
@@ -3355,7 +3312,7 @@
         <v>SUS.Piscina</v>
       </c>
       <c r="W8" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X8" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3365,19 +3322,19 @@
         <v>215</v>
       </c>
       <c r="Z8" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB8" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC8" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39">
         <v>9</v>
       </c>
@@ -3452,7 +3409,7 @@
         <v>SUS.Posto</v>
       </c>
       <c r="W9" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X9" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3462,19 +3419,19 @@
         <v>215</v>
       </c>
       <c r="Z9" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB9" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="39">
         <v>10</v>
       </c>
@@ -3549,7 +3506,7 @@
         <v>SUS.Quarto</v>
       </c>
       <c r="W10" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X10" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3559,19 +3516,19 @@
         <v>215</v>
       </c>
       <c r="Z10" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39">
         <v>11</v>
       </c>
@@ -3646,7 +3603,7 @@
         <v>SUS.Sala</v>
       </c>
       <c r="W11" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X11" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3656,19 +3613,19 @@
         <v>215</v>
       </c>
       <c r="Z11" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB11" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC11" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="39">
         <v>12</v>
       </c>
@@ -3743,7 +3700,7 @@
         <v>SUS.Zoneamento</v>
       </c>
       <c r="W12" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X12" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3753,19 +3710,19 @@
         <v>215</v>
       </c>
       <c r="Z12" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB12" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC12" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="39">
         <v>13</v>
       </c>
@@ -3840,7 +3797,7 @@
         <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="W13" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X13" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3850,19 +3807,19 @@
         <v>215</v>
       </c>
       <c r="Z13" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB13" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC13" s="42" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="39">
         <v>14</v>
       </c>
@@ -3937,7 +3894,7 @@
         <v>SUS.Setor</v>
       </c>
       <c r="W14" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X14" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3947,19 +3904,19 @@
         <v>215</v>
       </c>
       <c r="Z14" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="41" t="s">
         <v>216</v>
       </c>
       <c r="AB14" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC14" s="42" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39">
         <v>15</v>
       </c>
@@ -4034,7 +3991,7 @@
         <v>SUS.Robot</v>
       </c>
       <c r="W15" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X15" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4044,19 +4001,19 @@
         <v>217</v>
       </c>
       <c r="Z15" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="41" t="s">
         <v>174</v>
       </c>
       <c r="AB15" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="39">
         <v>16</v>
       </c>
@@ -4131,7 +4088,7 @@
         <v>SUS.Equipamento</v>
       </c>
       <c r="W16" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X16" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4141,19 +4098,19 @@
         <v>217</v>
       </c>
       <c r="Z16" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA16" s="41" t="s">
         <v>174</v>
       </c>
       <c r="AB16" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC16" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="39">
         <v>17</v>
       </c>
@@ -4228,7 +4185,7 @@
         <v>SUS.Dispositivo</v>
       </c>
       <c r="W17" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X17" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4238,19 +4195,19 @@
         <v>217</v>
       </c>
       <c r="Z17" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="41" t="s">
         <v>174</v>
       </c>
       <c r="AB17" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="39">
         <v>18</v>
       </c>
@@ -4325,7 +4282,7 @@
         <v>SUS.Instrumento</v>
       </c>
       <c r="W18" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X18" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4335,19 +4292,19 @@
         <v>217</v>
       </c>
       <c r="Z18" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA18" s="41" t="s">
         <v>174</v>
       </c>
       <c r="AB18" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="39">
         <v>19</v>
       </c>
@@ -4422,7 +4379,7 @@
         <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="W19" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X19" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4432,19 +4389,19 @@
         <v>176</v>
       </c>
       <c r="Z19" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="41" t="s">
         <v>177</v>
       </c>
       <c r="AB19" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="39">
         <v>20</v>
       </c>
@@ -4519,7 +4476,7 @@
         <v>SUS.Mobília</v>
       </c>
       <c r="W20" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X20" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4529,19 +4486,19 @@
         <v>176</v>
       </c>
       <c r="Z20" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="41" t="s">
         <v>177</v>
       </c>
       <c r="AB20" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="39">
         <v>21</v>
       </c>
@@ -4616,7 +4573,7 @@
         <v>SUS.Roupa</v>
       </c>
       <c r="W21" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X21" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4626,19 +4583,19 @@
         <v>176</v>
       </c>
       <c r="Z21" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="41" t="s">
         <v>177</v>
       </c>
       <c r="AB21" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC21" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="39">
         <v>22</v>
       </c>
@@ -4713,7 +4670,7 @@
         <v>SUS.Alimentação</v>
       </c>
       <c r="W22" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X22" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4723,36 +4680,36 @@
         <v>176</v>
       </c>
       <c r="Z22" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="41" t="s">
         <v>177</v>
       </c>
       <c r="AB22" s="42" t="s">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>23</v>
       </c>
       <c r="B23" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="55" t="s">
         <v>245</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>246</v>
       </c>
       <c r="D23" s="55" t="s">
         <v>247</v>
       </c>
       <c r="E23" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="F23" s="55" t="s">
         <v>248</v>
-      </c>
-      <c r="F23" s="55" t="s">
-        <v>249</v>
       </c>
       <c r="G23" s="66" t="s">
         <v>1</v>
@@ -4775,24 +4732,24 @@
       </c>
       <c r="M23" s="40" t="str">
         <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N23" s="40" t="str">
         <f t="shared" si="10"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O23" s="40" t="str">
         <f t="shared" si="10"/>
         <v>API Revit</v>
       </c>
       <c r="P23" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q23" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="Q23" s="41" t="s">
+      <c r="R23" s="41" t="s">
         <v>251</v>
-      </c>
-      <c r="R23" s="41" t="s">
-        <v>252</v>
       </c>
       <c r="S23" s="41" t="s">
         <v>1</v>
@@ -4803,14 +4760,14 @@
       </c>
       <c r="U23" s="41" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V23" s="42" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W23" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X23" s="44" t="str">
         <f t="shared" si="7"/>
@@ -4835,49 +4792,49 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="34" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="31" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:W22 W23">
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z22 AB2:XFD22 Y3:Y22 AA3:AA22">
-    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4893,19 +4850,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="30" t="s">
         <v>13</v>
       </c>
@@ -4970,7 +4927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -5038,7 +4995,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5054,14 +5011,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -5072,7 +5029,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -5085,7 +5042,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5097,25 +5054,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:W10"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" customWidth="1"/>
+    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3828125" style="33" customWidth="1"/>
+    <col min="6" max="6" width="5.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.3046875" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="58.42578125" style="22" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="33" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="3.7109375" style="72" customWidth="1"/>
+    <col min="9" max="9" width="58.3828125" style="22" customWidth="1"/>
+    <col min="10" max="10" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.3046875" style="33" customWidth="1"/>
+    <col min="12" max="12" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="3.69140625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -5186,7 +5143,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -5203,10 +5160,10 @@
         <v>180</v>
       </c>
       <c r="F2" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G2" s="69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H2" s="36" t="s">
         <v>84</v>
@@ -5257,7 +5214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -5274,10 +5231,10 @@
         <v>180</v>
       </c>
       <c r="F3" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G3" s="69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H3" s="36" t="s">
         <v>84</v>
@@ -5328,7 +5285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -5345,10 +5302,10 @@
         <v>180</v>
       </c>
       <c r="F4" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H4" s="36" t="s">
         <v>84</v>
@@ -5399,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -5416,10 +5373,10 @@
         <v>180</v>
       </c>
       <c r="F5" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G5" s="69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H5" s="36" t="s">
         <v>84</v>
@@ -5470,33 +5427,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>6</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D6" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E6" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="G6" s="69" t="s">
         <v>255</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>256</v>
       </c>
       <c r="H6" s="36" t="s">
         <v>84</v>
       </c>
       <c r="I6" s="69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J6" s="68" t="s">
         <v>1</v>
@@ -5509,7 +5466,7 @@
         <v>método.revit</v>
       </c>
       <c r="M6" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N6" s="74" t="s">
         <v>1</v>
@@ -5542,33 +5499,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <v>7</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D7" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E7" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="F7" s="68" t="s">
-        <v>255</v>
-      </c>
       <c r="G7" s="69" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H7" s="36" t="s">
         <v>84</v>
       </c>
       <c r="I7" s="69" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J7" s="68" t="s">
         <v>1</v>
@@ -5581,7 +5538,7 @@
         <v>método.revit</v>
       </c>
       <c r="M7" s="71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N7" s="74" t="s">
         <v>1</v>
@@ -5614,33 +5571,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>8</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D8" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E8" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="F8" s="68" t="s">
-        <v>255</v>
-      </c>
       <c r="G8" s="69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H8" s="36" t="s">
         <v>84</v>
       </c>
       <c r="I8" s="69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J8" s="68" t="s">
         <v>1</v>
@@ -5653,7 +5610,7 @@
         <v>método.revit</v>
       </c>
       <c r="M8" s="71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N8" s="74" t="s">
         <v>1</v>
@@ -5686,33 +5643,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>9</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E9" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="F9" s="68" t="s">
-        <v>255</v>
-      </c>
       <c r="G9" s="69" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H9" s="36" t="s">
         <v>84</v>
       </c>
       <c r="I9" s="69" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J9" s="68" t="s">
         <v>1</v>
@@ -5725,7 +5682,7 @@
         <v>método.revit</v>
       </c>
       <c r="M9" s="71" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N9" s="74" t="s">
         <v>1</v>
@@ -5758,33 +5715,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>10</v>
       </c>
       <c r="B10" s="67" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D10" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E10" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="F10" s="68" t="s">
-        <v>255</v>
-      </c>
       <c r="G10" s="69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>84</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J10" s="68" t="s">
         <v>1</v>
@@ -5797,7 +5754,7 @@
         <v>método.revit</v>
       </c>
       <c r="M10" s="71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N10" s="74" t="s">
         <v>1</v>
@@ -5832,41 +5789,41 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:B10">
-    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="17" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="40" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="36" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K10">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:M5 F1:I1 A1:E2 X1:XFD5 H2:I5 B3:E5 A3:A10 A11:M1048576 X11:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="11" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123665FB-7682-454E-998E-DC0E9E4CC26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472DEECA-444A-490C-BA11-269F51BF058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="293">
   <si>
     <t>Key</t>
   </si>
@@ -826,18 +826,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -905,6 +893,72 @@
   </si>
   <si>
     <t>"Volumes"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1084,12 +1138,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFDE75"/>
-        <bgColor rgb="FFFEF2CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
@@ -1138,18 +1186,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFDE75"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFDE75"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
@@ -1194,6 +1230,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -1249,7 +1303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1319,9 +1373,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1340,49 +1391,49 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1397,79 +1448,85 @@
     <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
     <dxf>
       <font>
         <b val="0"/>
@@ -1633,6 +1690,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2066,58 +2133,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="10.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3828125" customWidth="1"/>
-    <col min="2" max="2" width="48.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2125,11 +2192,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2137,177 +2204,177 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46264.577966550925</v>
-      </c>
-      <c r="C18" s="35" t="s">
+        <v>46268.701062037035</v>
+      </c>
+      <c r="C18" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>169</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>168</v>
       </c>
@@ -2315,11 +2382,11 @@
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="34" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>170</v>
       </c>
@@ -2327,33 +2394,33 @@
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="34" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="34" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>161</v>
       </c>
@@ -2361,161 +2428,161 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="34" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="B35" s="50" t="s">
+      <c r="B35" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="47" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="46" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="C39" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="47" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" s="46" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="34" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2535,2313 +2602,2785 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD27"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.69140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.69140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.84375" style="1"/>
+    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:30" s="3" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="J1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="K1" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="28" t="s">
+      <c r="Q1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="38" t="s">
+      <c r="R1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="T1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="U1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="V1" s="28" t="s">
+      <c r="V1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="28" t="s">
+      <c r="W1" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="X1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="Y1" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="Z1" s="28" t="s">
+      <c r="Z1" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="AA1" s="28" t="s">
+      <c r="AA1" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="AB1" s="28" t="s">
+      <c r="AB1" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="AC1" s="28" t="s">
+      <c r="AC1" s="27" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39">
+      <c r="AD1" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="38">
         <v>2</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="40" t="str">
+      <c r="G2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="39" t="str">
         <f t="shared" ref="L2:N2" si="0">CONCATENATE("", C2)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M2" s="40" t="str">
+      <c r="M2" s="39" t="str">
         <f t="shared" si="0"/>
         <v>SUS.Caderno</v>
       </c>
-      <c r="N2" s="40" t="str">
+      <c r="N2" s="39" t="str">
         <f t="shared" si="0"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="O2" s="40" t="str">
+      <c r="O2" s="39" t="str">
         <f t="shared" ref="O2" si="1">F2</f>
         <v>SUS.Volume</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="R2" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="S2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="40" t="str">
+      <c r="S2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="39" t="str">
         <f t="shared" ref="T2:V2" si="2">SUBSTITUTE(D2, "_", " ")</f>
         <v>SUS.Caderno</v>
       </c>
-      <c r="U2" s="40" t="str">
+      <c r="U2" s="39" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="V2" s="40" t="str">
+      <c r="V2" s="39" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Volume</v>
       </c>
-      <c r="W2" s="41" t="s">
+      <c r="W2" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X2" s="44" t="str">
+      <c r="X2" s="43" t="str">
         <f t="shared" ref="X2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="Y2" s="61" t="s">
+      <c r="Y2" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="Z2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="62" t="s">
+      <c r="Z2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="AB2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="42" t="s">
+      <c r="AB2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="41" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="39">
+      <c r="AD2" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="38">
         <v>3</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="73" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="40" t="str">
+      <c r="G3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="39" t="str">
         <f t="shared" ref="L3:N21" si="4">CONCATENATE("", C3)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M3" s="40" t="str">
+      <c r="M3" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N3" s="40" t="str">
+      <c r="N3" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O3" s="40" t="str">
+      <c r="O3" s="39" t="str">
         <f t="shared" ref="O3:O22" si="5">F3</f>
         <v>SUS.Area</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="R3" s="41" t="s">
+      <c r="R3" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="S3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="40" t="str">
+      <c r="S3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="39" t="str">
         <f t="shared" ref="T3:V21" si="6">SUBSTITUTE(D3, "_", " ")</f>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U3" s="40" t="str">
+      <c r="U3" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V3" s="40" t="str">
+      <c r="V3" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Area</v>
       </c>
-      <c r="W3" s="41" t="s">
+      <c r="W3" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X3" s="44" t="str">
-        <f t="shared" ref="X3:X23" si="7">CONCATENATE("Key-SUS-",A3)</f>
+      <c r="X3" s="43" t="str">
+        <f t="shared" ref="X3:X27" si="7">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
-      <c r="Y3" s="41" t="s">
+      <c r="Y3" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="41" t="s">
+      <c r="Z3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="42" t="s">
+      <c r="AB3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="39">
+      <c r="AD3" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="38">
         <v>4</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="E4" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="40" t="str">
+      <c r="G4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M4" s="40" t="str">
+      <c r="M4" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N4" s="40" t="str">
+      <c r="N4" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O4" s="40" t="str">
+      <c r="O4" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Box</v>
       </c>
-      <c r="P4" s="40" t="s">
+      <c r="P4" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="Q4" s="40" t="s">
+      <c r="Q4" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="41" t="s">
+      <c r="R4" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="S4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="40" t="str">
+      <c r="S4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U4" s="40" t="str">
+      <c r="U4" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V4" s="40" t="str">
+      <c r="V4" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Box</v>
       </c>
-      <c r="W4" s="41" t="s">
+      <c r="W4" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X4" s="44" t="str">
+      <c r="X4" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-4</v>
       </c>
-      <c r="Y4" s="41" t="s">
+      <c r="Y4" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="41" t="s">
+      <c r="Z4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="42" t="s">
+      <c r="AB4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="39">
+      <c r="AD4" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="38">
         <v>5</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="40" t="str">
+      <c r="G5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M5" s="40" t="str">
+      <c r="M5" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N5" s="40" t="str">
+      <c r="N5" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O5" s="40" t="str">
+      <c r="O5" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="P5" s="40" t="s">
+      <c r="P5" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="Q5" s="40" t="s">
+      <c r="Q5" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="R5" s="41" t="s">
+      <c r="R5" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="S5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="40" t="str">
+      <c r="S5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U5" s="40" t="str">
+      <c r="U5" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V5" s="40" t="str">
+      <c r="V5" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="W5" s="41" t="s">
+      <c r="W5" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X5" s="44" t="str">
+      <c r="X5" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-5</v>
       </c>
-      <c r="Y5" s="41" t="s">
+      <c r="Y5" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="41" t="s">
+      <c r="Z5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="42" t="s">
+      <c r="AB5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="39">
+      <c r="AD5" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="38">
         <v>6</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="73" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="40" t="str">
+      <c r="G6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M6" s="40" t="str">
+      <c r="M6" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N6" s="40" t="str">
+      <c r="N6" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O6" s="40" t="str">
+      <c r="O6" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="P6" s="40" t="s">
+      <c r="P6" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="Q6" s="40" t="s">
+      <c r="Q6" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="R6" s="41" t="s">
+      <c r="R6" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="S6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="40" t="str">
+      <c r="S6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U6" s="40" t="str">
+      <c r="U6" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V6" s="40" t="str">
+      <c r="V6" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="W6" s="41" t="s">
+      <c r="W6" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X6" s="44" t="str">
+      <c r="X6" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-6</v>
       </c>
-      <c r="Y6" s="41" t="s">
+      <c r="Y6" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="41" t="s">
+      <c r="Z6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="42" t="s">
+      <c r="AB6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="39">
+      <c r="AD6" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="38">
         <v>7</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="57" t="s">
+      <c r="D7" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="57" t="s">
+      <c r="E7" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="40" t="str">
+      <c r="G7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M7" s="40" t="str">
+      <c r="M7" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N7" s="40" t="str">
+      <c r="N7" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O7" s="40" t="str">
+      <c r="O7" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="P7" s="40" t="s">
+      <c r="P7" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="Q7" s="40" t="s">
+      <c r="Q7" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="R7" s="41" t="s">
+      <c r="R7" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="S7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="40" t="str">
+      <c r="S7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U7" s="40" t="str">
+      <c r="U7" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V7" s="40" t="str">
+      <c r="V7" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="W7" s="41" t="s">
+      <c r="W7" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X7" s="44" t="str">
+      <c r="X7" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-7</v>
       </c>
-      <c r="Y7" s="41" t="s">
+      <c r="Y7" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="41" t="s">
+      <c r="Z7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="42" t="s">
+      <c r="AB7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="39">
+      <c r="AD7" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="38">
         <v>8</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="57" t="s">
+      <c r="D8" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="57" t="s">
+      <c r="E8" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="G8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="40" t="str">
+      <c r="G8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M8" s="40" t="str">
+      <c r="M8" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N8" s="40" t="str">
+      <c r="N8" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O8" s="40" t="str">
+      <c r="O8" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="P8" s="40" t="s">
+      <c r="P8" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="Q8" s="40" t="s">
+      <c r="Q8" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="R8" s="41" t="s">
+      <c r="R8" s="40" t="s">
         <v>226</v>
       </c>
-      <c r="S8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="40" t="str">
+      <c r="S8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U8" s="40" t="str">
+      <c r="U8" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V8" s="40" t="str">
+      <c r="V8" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="W8" s="41" t="s">
+      <c r="W8" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X8" s="44" t="str">
+      <c r="X8" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-8</v>
       </c>
-      <c r="Y8" s="41" t="s">
+      <c r="Y8" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="41" t="s">
+      <c r="Z8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="42" t="s">
+      <c r="AB8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39">
+      <c r="AD8" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="38">
         <v>9</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="40" t="str">
+      <c r="G9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M9" s="40" t="str">
+      <c r="M9" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N9" s="40" t="str">
+      <c r="N9" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O9" s="40" t="str">
+      <c r="O9" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="P9" s="40" t="s">
+      <c r="P9" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="Q9" s="40" t="s">
+      <c r="Q9" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="R9" s="41" t="s">
+      <c r="R9" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="S9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="40" t="str">
+      <c r="S9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U9" s="40" t="str">
+      <c r="U9" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V9" s="40" t="str">
+      <c r="V9" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="W9" s="41" t="s">
+      <c r="W9" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X9" s="44" t="str">
+      <c r="X9" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-9</v>
       </c>
-      <c r="Y9" s="41" t="s">
+      <c r="Y9" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="41" t="s">
+      <c r="Z9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="42" t="s">
+      <c r="AB9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="39">
+      <c r="AD9" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="38">
         <v>10</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="G10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="40" t="str">
+      <c r="G10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M10" s="40" t="str">
+      <c r="M10" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N10" s="40" t="str">
+      <c r="N10" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O10" s="40" t="str">
+      <c r="O10" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="P10" s="40" t="s">
+      <c r="P10" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="Q10" s="40" t="s">
+      <c r="Q10" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="R10" s="41" t="s">
+      <c r="R10" s="40" t="s">
         <v>228</v>
       </c>
-      <c r="S10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="40" t="str">
+      <c r="S10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U10" s="40" t="str">
+      <c r="U10" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V10" s="40" t="str">
+      <c r="V10" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="W10" s="41" t="s">
+      <c r="W10" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X10" s="44" t="str">
+      <c r="X10" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-10</v>
       </c>
-      <c r="Y10" s="41" t="s">
+      <c r="Y10" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="41" t="s">
+      <c r="Z10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="42" t="s">
+      <c r="AB10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="39">
+      <c r="AD10" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="38">
         <v>11</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="57" t="s">
+      <c r="D11" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="57" t="s">
+      <c r="E11" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="G11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="40" t="str">
+      <c r="G11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M11" s="40" t="str">
+      <c r="M11" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N11" s="40" t="str">
+      <c r="N11" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O11" s="40" t="str">
+      <c r="O11" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="P11" s="40" t="s">
+      <c r="P11" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="Q11" s="40" t="s">
+      <c r="Q11" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="R11" s="41" t="s">
+      <c r="R11" s="40" t="s">
         <v>229</v>
       </c>
-      <c r="S11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="40" t="str">
+      <c r="S11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U11" s="40" t="str">
+      <c r="U11" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V11" s="40" t="str">
+      <c r="V11" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="W11" s="41" t="s">
+      <c r="W11" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X11" s="44" t="str">
+      <c r="X11" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-11</v>
       </c>
-      <c r="Y11" s="41" t="s">
+      <c r="Y11" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="41" t="s">
+      <c r="Z11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="42" t="s">
+      <c r="AB11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="39">
+      <c r="AD11" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="38">
         <v>12</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="60" t="s">
+      <c r="F12" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="40" t="str">
+      <c r="G12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M12" s="40" t="str">
+      <c r="M12" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N12" s="40" t="str">
+      <c r="N12" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O12" s="40" t="str">
+      <c r="O12" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="P12" s="40" t="s">
+      <c r="P12" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="Q12" s="40" t="s">
+      <c r="Q12" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="R12" s="41" t="s">
+      <c r="R12" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="S12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="40" t="str">
+      <c r="S12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U12" s="40" t="str">
+      <c r="U12" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V12" s="40" t="str">
+      <c r="V12" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="W12" s="41" t="s">
+      <c r="W12" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X12" s="44" t="str">
+      <c r="X12" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-12</v>
       </c>
-      <c r="Y12" s="41" t="s">
+      <c r="Y12" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="41" t="s">
+      <c r="Z12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="42" t="s">
+      <c r="AB12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="41" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="39">
+      <c r="AD12" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="38">
         <v>13</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="40" t="str">
+      <c r="G13" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M13" s="40" t="str">
+      <c r="M13" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N13" s="40" t="str">
+      <c r="N13" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O13" s="40" t="str">
+      <c r="O13" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="P13" s="40" t="s">
+      <c r="P13" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="Q13" s="40" t="s">
+      <c r="Q13" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="R13" s="41" t="s">
+      <c r="R13" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="S13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="40" t="str">
+      <c r="S13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U13" s="40" t="str">
+      <c r="U13" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V13" s="40" t="str">
+      <c r="V13" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="W13" s="41" t="s">
+      <c r="W13" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X13" s="44" t="str">
+      <c r="X13" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-13</v>
       </c>
-      <c r="Y13" s="41" t="s">
+      <c r="Y13" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="41" t="s">
+      <c r="Z13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="42" t="s">
+      <c r="AB13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="41" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="39">
+      <c r="AD13" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="38">
         <v>14</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D14" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="40" t="str">
+      <c r="G14" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M14" s="40" t="str">
+      <c r="M14" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N14" s="40" t="str">
+      <c r="N14" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O14" s="40" t="str">
+      <c r="O14" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="P14" s="40" t="s">
+      <c r="P14" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="Q14" s="40" t="s">
+      <c r="Q14" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="R14" s="41" t="s">
+      <c r="R14" s="40" t="s">
         <v>232</v>
       </c>
-      <c r="S14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="40" t="str">
+      <c r="S14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U14" s="40" t="str">
+      <c r="U14" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V14" s="40" t="str">
+      <c r="V14" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="W14" s="41" t="s">
+      <c r="W14" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X14" s="44" t="str">
+      <c r="X14" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-14</v>
       </c>
-      <c r="Y14" s="41" t="s">
+      <c r="Y14" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="Z14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="41" t="s">
+      <c r="Z14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="42" t="s">
+      <c r="AB14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="41" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="39">
+      <c r="AD14" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="38">
         <v>15</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="57" t="s">
+      <c r="D15" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="57" t="s">
+      <c r="E15" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="40" t="str">
+      <c r="G15" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M15" s="40" t="str">
+      <c r="M15" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N15" s="40" t="str">
+      <c r="N15" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O15" s="40" t="str">
+      <c r="O15" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="P15" s="40" t="s">
+      <c r="P15" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="Q15" s="40" t="s">
+      <c r="Q15" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="R15" s="41" t="s">
+      <c r="R15" s="40" t="s">
         <v>233</v>
       </c>
-      <c r="S15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="40" t="str">
+      <c r="S15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U15" s="40" t="str">
+      <c r="U15" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V15" s="40" t="str">
+      <c r="V15" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="W15" s="41" t="s">
+      <c r="W15" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X15" s="44" t="str">
+      <c r="X15" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-15</v>
       </c>
-      <c r="Y15" s="41" t="s">
+      <c r="Y15" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="Z15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="41" t="s">
+      <c r="Z15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="AB15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="42" t="s">
+      <c r="AB15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="39">
+      <c r="AD15" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="38">
         <v>16</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="40" t="str">
+      <c r="G16" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M16" s="40" t="str">
+      <c r="M16" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N16" s="40" t="str">
+      <c r="N16" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O16" s="40" t="str">
+      <c r="O16" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="P16" s="40" t="s">
+      <c r="P16" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="Q16" s="40" t="s">
+      <c r="Q16" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="R16" s="41" t="s">
+      <c r="R16" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="S16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="40" t="str">
+      <c r="S16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U16" s="40" t="str">
+      <c r="U16" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V16" s="40" t="str">
+      <c r="V16" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="W16" s="41" t="s">
+      <c r="W16" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X16" s="44" t="str">
+      <c r="X16" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-16</v>
       </c>
-      <c r="Y16" s="41" t="s">
+      <c r="Y16" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="Z16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="41" t="s">
+      <c r="Z16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="AB16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="42" t="s">
+      <c r="AB16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="39">
+      <c r="AD16" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="38">
         <v>17</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="F17" s="60" t="s">
+      <c r="F17" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="40" t="str">
+      <c r="G17" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M17" s="40" t="str">
+      <c r="M17" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N17" s="40" t="str">
+      <c r="N17" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O17" s="40" t="str">
+      <c r="O17" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="P17" s="40" t="s">
+      <c r="P17" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="Q17" s="40" t="s">
+      <c r="Q17" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="R17" s="41" t="s">
+      <c r="R17" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="S17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="40" t="str">
+      <c r="S17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U17" s="40" t="str">
+      <c r="U17" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V17" s="40" t="str">
+      <c r="V17" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="W17" s="41" t="s">
+      <c r="W17" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X17" s="44" t="str">
+      <c r="X17" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-17</v>
       </c>
-      <c r="Y17" s="41" t="s">
+      <c r="Y17" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="Z17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="41" t="s">
+      <c r="Z17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="AB17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="42" t="s">
+      <c r="AB17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="39">
+      <c r="AD17" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="38">
         <v>18</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="60" t="s">
+      <c r="F18" s="75" t="s">
         <v>142</v>
       </c>
-      <c r="G18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="40" t="str">
+      <c r="G18" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M18" s="40" t="str">
+      <c r="M18" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N18" s="40" t="str">
+      <c r="N18" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O18" s="40" t="str">
+      <c r="O18" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="P18" s="40" t="s">
+      <c r="P18" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="Q18" s="40" t="s">
+      <c r="Q18" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="R18" s="41" t="s">
+      <c r="R18" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="S18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="40" t="str">
+      <c r="S18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U18" s="40" t="str">
+      <c r="U18" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V18" s="40" t="str">
+      <c r="V18" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="W18" s="41" t="s">
+      <c r="W18" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X18" s="44" t="str">
+      <c r="X18" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-18</v>
       </c>
-      <c r="Y18" s="41" t="s">
+      <c r="Y18" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="Z18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="41" t="s">
+      <c r="Z18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="AB18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="42" t="s">
+      <c r="AB18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="39">
+      <c r="AD18" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38">
         <v>19</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="57" t="s">
+      <c r="D19" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="57" t="s">
+      <c r="E19" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="60" t="s">
+      <c r="F19" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="40" t="str">
+      <c r="G19" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M19" s="40" t="str">
+      <c r="M19" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N19" s="40" t="str">
+      <c r="N19" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O19" s="40" t="str">
+      <c r="O19" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="P19" s="40" t="s">
+      <c r="P19" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="Q19" s="40" t="s">
+      <c r="Q19" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="R19" s="41" t="s">
+      <c r="R19" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="S19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="40" t="str">
+      <c r="S19" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U19" s="40" t="str">
+      <c r="U19" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V19" s="40" t="str">
+      <c r="V19" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="W19" s="41" t="s">
+      <c r="W19" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X19" s="44" t="str">
+      <c r="X19" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-19</v>
       </c>
-      <c r="Y19" s="41" t="s">
+      <c r="Y19" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="Z19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="41" t="s">
+      <c r="Z19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="AB19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="42" t="s">
+      <c r="AB19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="39">
+      <c r="AD19" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="38">
         <v>20</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="60" t="s">
+      <c r="F20" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="40" t="str">
+      <c r="G20" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M20" s="40" t="str">
+      <c r="M20" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N20" s="40" t="str">
+      <c r="N20" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O20" s="40" t="str">
+      <c r="O20" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="P20" s="40" t="s">
+      <c r="P20" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="Q20" s="40" t="s">
+      <c r="Q20" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="R20" s="41" t="s">
+      <c r="R20" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="S20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T20" s="40" t="str">
+      <c r="S20" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U20" s="40" t="str">
+      <c r="U20" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V20" s="40" t="str">
+      <c r="V20" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="W20" s="41" t="s">
+      <c r="W20" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X20" s="44" t="str">
+      <c r="X20" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-20</v>
       </c>
-      <c r="Y20" s="41" t="s">
+      <c r="Y20" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="Z20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="41" t="s">
+      <c r="Z20" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="AB20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="42" t="s">
+      <c r="AB20" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="39">
+      <c r="AD20" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="38">
         <v>21</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="60" t="s">
+      <c r="F21" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="G21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="40" t="str">
+      <c r="G21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M21" s="40" t="str">
+      <c r="M21" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N21" s="40" t="str">
+      <c r="N21" s="39" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O21" s="40" t="str">
+      <c r="O21" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="P21" s="40" t="s">
+      <c r="P21" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="Q21" s="40" t="s">
+      <c r="Q21" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="R21" s="41" t="s">
+      <c r="R21" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="S21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="40" t="str">
+      <c r="S21" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U21" s="40" t="str">
+      <c r="U21" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V21" s="40" t="str">
+      <c r="V21" s="39" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="W21" s="41" t="s">
+      <c r="W21" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X21" s="44" t="str">
+      <c r="X21" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-21</v>
       </c>
-      <c r="Y21" s="41" t="s">
+      <c r="Y21" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="Z21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="41" t="s">
+      <c r="Z21" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="AB21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="42" t="s">
+      <c r="AB21" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="39">
+      <c r="AD21" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="38">
         <v>22</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="40" t="str">
+      <c r="G22" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="39" t="str">
         <f t="shared" ref="L22:N22" si="8">CONCATENATE("", C22)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M22" s="40" t="str">
+      <c r="M22" s="39" t="str">
         <f t="shared" si="8"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N22" s="40" t="str">
+      <c r="N22" s="39" t="str">
         <f t="shared" si="8"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O22" s="40" t="str">
+      <c r="O22" s="39" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="P22" s="40" t="s">
+      <c r="P22" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="Q22" s="40" t="s">
+      <c r="Q22" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="R22" s="41" t="s">
+      <c r="R22" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="S22" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="40" t="str">
+      <c r="S22" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="39" t="str">
         <f t="shared" ref="T22:V22" si="9">SUBSTITUTE(D22, "_", " ")</f>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U22" s="40" t="str">
+      <c r="U22" s="39" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V22" s="40" t="str">
+      <c r="V22" s="39" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="W22" s="41" t="s">
+      <c r="W22" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X22" s="44" t="str">
+      <c r="X22" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-22</v>
       </c>
-      <c r="Y22" s="41" t="s">
+      <c r="Y22" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="Z22" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="41" t="s">
+      <c r="Z22" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="AB22" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="42" t="s">
+      <c r="AB22" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="41" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39">
+      <c r="AD22" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="38">
         <v>23</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="68" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="70" t="s">
         <v>245</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="70" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="55" t="s">
+      <c r="E23" s="70" t="s">
         <v>246</v>
       </c>
-      <c r="F23" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="G23" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="40" t="str">
-        <f t="shared" ref="L23:O23" si="10">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
+      <c r="F23" s="70" t="s">
+        <v>271</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="39" t="str">
+        <f t="shared" ref="L23:O27" si="10">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M23" s="40" t="str">
+      <c r="M23" s="39" t="str">
         <f t="shared" si="10"/>
         <v>Macros</v>
       </c>
-      <c r="N23" s="40" t="str">
+      <c r="N23" s="39" t="str">
         <f t="shared" si="10"/>
         <v>Métodos</v>
       </c>
-      <c r="O23" s="40" t="str">
+      <c r="O23" s="39" t="str">
         <f t="shared" si="10"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P23" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q23" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="R23" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="S23" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T23" s="41" t="str">
-        <f t="shared" ref="T23:V23" si="11">SUBSTITUTE(C23, ".", " ")</f>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P23" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q23" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="R23" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="S23" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="40" t="str">
+        <f t="shared" ref="T23:V27" si="11">SUBSTITUTE(C23, ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="U23" s="41" t="str">
+      <c r="U23" s="40" t="str">
         <f t="shared" si="11"/>
         <v>Macros</v>
       </c>
-      <c r="V23" s="42" t="str">
+      <c r="V23" s="41" t="str">
         <f t="shared" si="11"/>
         <v>Métodos</v>
       </c>
-      <c r="W23" s="41" t="s">
+      <c r="W23" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="X23" s="44" t="str">
+      <c r="X23" s="43" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-23</v>
       </c>
-      <c r="Y23" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="63" t="s">
+      <c r="Y23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="38">
+        <v>24</v>
+      </c>
+      <c r="B24" s="68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="D24" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E24" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F24" s="70" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>De API</v>
+      </c>
+      <c r="M24" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Macros</v>
+      </c>
+      <c r="N24" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O24" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P24" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q24" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="R24" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="S24" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="U24" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="V24" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W24" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="X24" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-SUS-24</v>
+      </c>
+      <c r="Y24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="38">
+        <v>25</v>
+      </c>
+      <c r="B25" s="68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="70" t="s">
+        <v>279</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>De API</v>
+      </c>
+      <c r="M25" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Macros</v>
+      </c>
+      <c r="N25" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O25" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P25" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q25" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="R25" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="S25" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="U25" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="V25" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W25" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="X25" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-SUS-25</v>
+      </c>
+      <c r="Y25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="38">
+        <v>26</v>
+      </c>
+      <c r="B26" s="68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E26" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F26" s="70" t="s">
+        <v>283</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>De API</v>
+      </c>
+      <c r="M26" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Macros</v>
+      </c>
+      <c r="N26" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O26" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P26" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q26" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="R26" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="S26" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T26" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="U26" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="V26" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W26" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="X26" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-SUS-26</v>
+      </c>
+      <c r="Y26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="38">
+        <v>27</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E27" s="70" t="s">
+        <v>287</v>
+      </c>
+      <c r="F27" s="70" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>De API</v>
+      </c>
+      <c r="M27" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Macros</v>
+      </c>
+      <c r="N27" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O27" s="39" t="str">
+        <f t="shared" si="10"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P27" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q27" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="R27" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S27" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>De API</v>
+      </c>
+      <c r="U27" s="40" t="str">
+        <f t="shared" si="11"/>
+        <v>Macros</v>
+      </c>
+      <c r="V27" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W27" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="X27" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-SUS-27</v>
+      </c>
+      <c r="Y27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="40" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="29" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E27:F27">
+    <cfRule type="duplicateValues" dxfId="29" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="28" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
+  <conditionalFormatting sqref="F23:F26">
     <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R22">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:W22 W23">
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+  <conditionalFormatting sqref="T2:W22 W23:W27">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z22 AB2:XFD22 Y3:Y22 AA3:AA22">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+  <conditionalFormatting sqref="AC2:AC22 AE2:XFD22 Y3:Y22 AA3:AA22">
+    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="S1:X1 AD1:XFD1 AC24:XFD1048576 A24:P1048576 A1:P1 AA24:AA1048576 S24:Y1048576" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AE1:XFD1 AC28:XFD1048576 A28:P1048576 A1:P1 AA28:AA1048576 S28:Y1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4850,85 +5389,85 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.3828125" style="5"/>
+    <col min="22" max="16384" width="5.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="31" t="s">
+      <c r="Q1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="T1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="30" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="29">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -5011,14 +5550,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -5029,7 +5568,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -5054,25 +5593,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842A128A-C40E-43D6-A351-FFD2E9954DB9}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:W10"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.15234375" customWidth="1"/>
-    <col min="4" max="4" width="4.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.3828125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="5.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="32" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="32" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="58.3828125" style="22" customWidth="1"/>
-    <col min="10" max="10" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.3046875" style="33" customWidth="1"/>
-    <col min="12" max="12" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="3.69140625" style="72" customWidth="1"/>
+    <col min="9" max="9" width="58.42578125" style="22" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="32" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="3.7109375" style="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>24</v>
       </c>
@@ -5112,748 +5651,748 @@
       <c r="M1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="73" t="s">
+      <c r="N1" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="73" t="s">
+      <c r="O1" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="73" t="s">
+      <c r="P1" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="73" t="s">
+      <c r="Q1" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="73" t="s">
+      <c r="R1" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="73" t="s">
+      <c r="S1" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="73" t="s">
+      <c r="T1" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="U1" s="73" t="s">
+      <c r="U1" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="V1" s="73" t="s">
+      <c r="V1" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="73" t="s">
+      <c r="W1" s="64" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G2" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="H2" s="36" t="s">
+      <c r="F2" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="H2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="L2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="F3" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G3" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="H3" s="36" t="s">
+      <c r="F3" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="H3" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="L3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W3" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G4" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="H4" s="36" t="s">
+      <c r="F4" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="H4" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="L4" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G5" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="H5" s="36" t="s">
+      <c r="F5" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="H5" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="L5" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="23">
         <v>6</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="58" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" s="70" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>251</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="60" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D6" s="68" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="69" t="s">
-        <v>256</v>
-      </c>
-      <c r="J6" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="70" t="str">
+      <c r="J6" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="61" t="str">
         <f t="shared" ref="L6:L10" si="0">IF(M6="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="M6" s="71" t="s">
-        <v>257</v>
-      </c>
-      <c r="N6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="62" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="23">
         <v>7</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D7" s="68" t="s">
+      <c r="B7" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>283</v>
+      </c>
+      <c r="D7" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="69" t="s">
-        <v>253</v>
-      </c>
-      <c r="F7" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G7" s="69" t="s">
-        <v>259</v>
-      </c>
-      <c r="H7" s="36" t="s">
+      <c r="E7" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>255</v>
+      </c>
+      <c r="H7" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="J7" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="70" t="str">
+      <c r="I7" s="60" t="s">
+        <v>256</v>
+      </c>
+      <c r="J7" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M7" s="71" t="s">
-        <v>261</v>
-      </c>
-      <c r="N7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="N7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23">
         <v>8</v>
       </c>
-      <c r="B8" s="67" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D8" s="68" t="s">
+      <c r="B8" s="58" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="69" t="s">
-        <v>253</v>
-      </c>
-      <c r="F8" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G8" s="69" t="s">
-        <v>263</v>
-      </c>
-      <c r="H8" s="36" t="s">
+      <c r="E8" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>259</v>
+      </c>
+      <c r="H8" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="69" t="s">
-        <v>264</v>
-      </c>
-      <c r="J8" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="70" t="str">
+      <c r="I8" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="J8" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M8" s="71" t="s">
-        <v>265</v>
-      </c>
-      <c r="N8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="N8" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="23">
         <v>9</v>
       </c>
-      <c r="B9" s="67" t="s">
-        <v>266</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D9" s="68" t="s">
+      <c r="B9" s="58" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="70" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="69" t="s">
-        <v>253</v>
-      </c>
-      <c r="F9" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G9" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="H9" s="36" t="s">
+      <c r="E9" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="H9" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="69" t="s">
-        <v>268</v>
-      </c>
-      <c r="J9" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="70" t="str">
+      <c r="I9" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="J9" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M9" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="N9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="62" t="s">
+        <v>265</v>
+      </c>
+      <c r="N9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23">
         <v>10</v>
       </c>
-      <c r="B10" s="67" t="s">
-        <v>270</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="68" t="s">
+      <c r="B10" s="58" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="70" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="69" t="s">
-        <v>253</v>
-      </c>
-      <c r="F10" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="G10" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="H10" s="36" t="s">
+      <c r="E10" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G10" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="H10" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="69" t="s">
-        <v>272</v>
-      </c>
-      <c r="J10" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="70" t="str">
+      <c r="I10" s="60" t="s">
+        <v>268</v>
+      </c>
+      <c r="J10" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M10" s="71" t="s">
-        <v>273</v>
-      </c>
-      <c r="N10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="75" t="s">
+      <c r="M10" s="62" t="s">
+        <v>269</v>
+      </c>
+      <c r="N10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="66" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:B10">
-    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="12" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="41" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="10" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="9" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="34" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K10">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:M5 F1:I1 A1:E2 X1:XFD5 H2:I5 B3:E5 A3:A10 A11:M1048576 X11:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:W1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472DEECA-444A-490C-BA11-269F51BF058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E3B8CD-94FA-491E-9A2B-FD1741527234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="312">
   <si>
     <t>Key</t>
   </si>
@@ -637,87 +637,45 @@
     <t>"Volume 2 - Internação e Apoio ao Diagnóstico e à Terapia (Reabilitação)"</t>
   </si>
   <si>
-    <t>Fonte1</t>
-  </si>
-  <si>
     <t>https://brasil.un.org/pt-br/sdgs</t>
   </si>
   <si>
-    <t>Fonte2</t>
-  </si>
-  <si>
     <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
   </si>
   <si>
-    <t>Fonte3</t>
-  </si>
-  <si>
     <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
   </si>
   <si>
-    <t>FonteVegetação1</t>
-  </si>
-  <si>
     <t>https://museunacional.ufrj.br/hortobotanico</t>
   </si>
   <si>
-    <t>FonteVegetação2</t>
-  </si>
-  <si>
     <t>https://www.embrapa.br/florestas/publicacoes</t>
   </si>
   <si>
-    <t>FonteVegetação3</t>
-  </si>
-  <si>
     <t>https://www.arvoresgigantes.org</t>
   </si>
   <si>
-    <t>FonteVegetação4</t>
-  </si>
-  <si>
     <t>https://www.scielo.br/j/abb</t>
   </si>
   <si>
-    <t>FonteVegetação5</t>
-  </si>
-  <si>
     <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
   </si>
   <si>
-    <t>FonteVegetação6</t>
-  </si>
-  <si>
     <t>https://botanicasaopaulo.org</t>
   </si>
   <si>
-    <t>FonteVegetação7</t>
-  </si>
-  <si>
     <t>https://pesquisa.in.gov.br/imprensa</t>
   </si>
   <si>
-    <t>FonteVegetação8</t>
-  </si>
-  <si>
     <t>https://mapas.florestal.gov.br</t>
   </si>
   <si>
-    <t>FonteTSB</t>
-  </si>
-  <si>
     <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
   </si>
   <si>
-    <t>FonteSINAPI</t>
-  </si>
-  <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
   <si>
-    <t>FonteSomaSUS</t>
-  </si>
-  <si>
     <t>https://somasus.saude.gov.br/sistema/home</t>
   </si>
   <si>
@@ -814,18 +772,6 @@
     <t>Hospitalar Público</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -943,9 +889,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -959,6 +902,120 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.01</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.02</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.03</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.04</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.01</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.02</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.03</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.04</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.05</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.06</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.07</t>
+  </si>
+  <si>
+    <t>Fonte.Vegetação.08</t>
+  </si>
+  <si>
+    <t>Fonte.SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.Saúde.01</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.Saúde.02</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.Saúde.03</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>Fonte.Brasil.Saúde.04</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>Fonte.NBR.01</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>Fonte.NBR.02</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>Fonte.NBR.03</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>Fonte.NBR.04</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>Fonte.NBR.05</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Fonte.Bombeiros.01</t>
+  </si>
+  <si>
+    <t>IT Bombeiros (estadual). Segurança contra incêndio. Varia por estado — consultar VISA local.</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1120,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1241,13 +1298,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor theme="0"/>
+        <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor rgb="FFFEF2CB"/>
+        <fgColor rgb="FFFFDE75"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFDE75"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1303,7 +1366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1382,9 +1445,6 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1433,15 +1493,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1456,9 +1513,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1494,39 +1548,75 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="35">
     <dxf>
       <font>
         <b val="0"/>
@@ -1693,6 +1783,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1790,6 +1888,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2132,10 +2238,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2147,7 +2253,7 @@
       <c r="B1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2158,7 +2264,7 @@
       <c r="B2" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2169,7 +2275,7 @@
       <c r="B3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2180,7 +2286,7 @@
       <c r="B4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2192,7 +2298,7 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2204,7 +2310,7 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2215,7 +2321,7 @@
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2226,7 +2332,7 @@
       <c r="B8" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2237,7 +2343,7 @@
       <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2248,7 +2354,7 @@
       <c r="B10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2259,7 +2365,7 @@
       <c r="B11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2270,7 +2376,7 @@
       <c r="B12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2281,7 +2387,7 @@
       <c r="B13" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2292,7 +2398,7 @@
       <c r="B14" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2303,7 +2409,7 @@
       <c r="B15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2314,7 +2420,7 @@
       <c r="B16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2325,7 +2431,7 @@
       <c r="B17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2335,9 +2441,9 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46268.701062037035</v>
-      </c>
-      <c r="C18" s="34" t="s">
+        <v>46274.303017129627</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2348,7 +2454,7 @@
       <c r="B19" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2359,7 +2465,7 @@
       <c r="B20" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2370,7 +2476,7 @@
       <c r="B21" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2382,7 +2488,7 @@
         <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
         <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="33" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2394,7 +2500,7 @@
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="33" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2405,7 +2511,7 @@
       <c r="B24" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="33" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2416,7 +2522,7 @@
       <c r="B25" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="33" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2428,172 +2534,272 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="33" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B27" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="C27" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B28" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C28" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="29" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="48" t="s">
+      <c r="C29" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C31" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="32" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B32" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="C32" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B33" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C33" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="14" t="s">
+    <row r="34" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B34" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="C34" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B35" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C35" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="14" t="s">
+    <row r="36" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B36" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="C36" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B37" s="79" t="s">
         <v>194</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C37" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="14" t="s">
+    <row r="38" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B38" s="78" t="s">
         <v>195</v>
       </c>
-      <c r="B32" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="C32" s="34" t="s">
+      <c r="C38" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="14" t="s">
+    <row r="39" spans="1:3" s="80" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B39" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="C39" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B40" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C40" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B34" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="C34" s="34" t="s">
+    <row r="41" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B41" s="82" t="s">
+        <v>295</v>
+      </c>
+      <c r="C41" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="B35" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C35" s="34" t="s">
+    <row r="42" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B42" s="83" t="s">
+        <v>297</v>
+      </c>
+      <c r="C42" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="C36" s="34" t="s">
+    <row r="43" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B43" s="83" t="s">
+        <v>299</v>
+      </c>
+      <c r="C43" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="44" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="B37" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="C37" s="34" t="s">
+    <row r="44" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="83" t="s">
+        <v>301</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="C38" s="34" t="s">
+    <row r="45" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B45" s="83" t="s">
+        <v>303</v>
+      </c>
+      <c r="C45" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="46" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="C39" s="34" t="s">
+    <row r="46" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B46" s="83" t="s">
+        <v>305</v>
+      </c>
+      <c r="C46" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="46" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="B40" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="C40" s="34" t="s">
+    <row r="47" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="B47" s="83" t="s">
+        <v>307</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" s="83" t="s">
+        <v>309</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="B49" s="83" t="s">
+        <v>311</v>
+      </c>
+      <c r="C49" s="33" t="s">
         <v>164</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B27" r:id="rId1" xr:uid="{5459870A-EA88-4D94-AECD-FB25ABC9E3FC}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{517B939F-01A7-4003-85A6-6C122E4F286F}"/>
-    <hyperlink ref="B28" r:id="rId3" xr:uid="{79B7ECCC-039C-4CB2-AB5A-86C571F94E9E}"/>
-    <hyperlink ref="B38" r:id="rId4" xr:uid="{601C1702-E1F4-4441-A0A3-884453A34A55}"/>
-    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{980343AA-51B7-4173-B919-F6A27B8E831B}"/>
-    <hyperlink ref="B40" r:id="rId6" xr:uid="{D7BD13C7-FFD2-43AB-8F15-8A3AFF357A49}"/>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{88DD90D0-931F-4AAC-AE7E-516F82689E7D}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{645F0605-0703-420A-BEE4-A645E90ACDFC}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{B08EA68F-728E-4768-B845-95C20330440C}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{D4029F2D-4B86-4D86-9A84-0D744B69DFE3}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{71DCF592-0061-42CE-9049-9B3CB669E301}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{32BAD505-06E3-40A9-A25F-6A2E6C77E9CE}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{D24CD502-BC2F-4045-AE05-736D65D9F826}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2606,31 +2812,32 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
+    <col min="7" max="11" width="7.5703125" style="1" customWidth="1"/>
     <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="8" customWidth="1"/>
+    <col min="16" max="16" width="40" style="1" customWidth="1"/>
+    <col min="17" max="17" width="38" style="1" customWidth="1"/>
+    <col min="18" max="18" width="37.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="76" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5703125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="11" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="36" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.5703125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="37.140625" style="1" customWidth="1"/>
     <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.7109375" style="1" customWidth="1"/>
     <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.85546875" style="1"/>
+    <col min="30" max="30" width="4.5703125" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="3" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -2652,19 +2859,19 @@
       <c r="F1" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="51" t="s">
         <v>35</v>
       </c>
       <c r="L1" s="27" t="s">
@@ -2685,10 +2892,10 @@
       <c r="Q1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="S1" s="28" t="s">
+      <c r="S1" s="75" t="s">
         <v>85</v>
       </c>
       <c r="T1" s="27" t="s">
@@ -2703,2677 +2910,2685 @@
       <c r="W1" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="X1" s="42" t="s">
+      <c r="X1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="27" t="s">
         <v>97</v>
       </c>
       <c r="Z1" s="27" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="AC1" s="27" t="s">
         <v>98</v>
       </c>
       <c r="AD1" s="27" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38">
+      <c r="A2" s="37">
         <v>2</v>
       </c>
-      <c r="B2" s="68" t="s">
-        <v>213</v>
+      <c r="B2" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C2" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="70" t="s">
-        <v>214</v>
-      </c>
-      <c r="F2" s="71" t="s">
+      <c r="E2" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="39" t="str">
+      <c r="G2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="38" t="str">
         <f t="shared" ref="L2:N2" si="0">CONCATENATE("", C2)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M2" s="39" t="str">
+      <c r="M2" s="38" t="str">
         <f t="shared" si="0"/>
         <v>SUS.Caderno</v>
       </c>
-      <c r="N2" s="39" t="str">
+      <c r="N2" s="38" t="str">
         <f t="shared" si="0"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="O2" s="39" t="str">
+      <c r="O2" s="38" t="str">
         <f t="shared" ref="O2" si="1">F2</f>
         <v>SUS.Volume</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="R2" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="S2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="39" t="str">
+      <c r="R2" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="S2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="38" t="str">
         <f t="shared" ref="T2:V2" si="2">SUBSTITUTE(D2, "_", " ")</f>
         <v>SUS.Caderno</v>
       </c>
-      <c r="U2" s="39" t="str">
+      <c r="U2" s="38" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Informação</v>
       </c>
-      <c r="V2" s="39" t="str">
+      <c r="V2" s="38" t="str">
         <f t="shared" si="2"/>
         <v>SUS.Volume</v>
       </c>
-      <c r="W2" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X2" s="43" t="str">
+      <c r="W2" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X2" s="42" t="str">
         <f t="shared" ref="X2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="Y2" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="41" t="s">
+      <c r="Y2" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AD2" s="40" t="s">
+      <c r="AD2" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="38">
+      <c r="A3" s="37">
         <v>3</v>
       </c>
-      <c r="B3" s="68" t="s">
-        <v>213</v>
+      <c r="B3" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C3" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="39" t="str">
+      <c r="G3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="38" t="str">
         <f t="shared" ref="L3:N21" si="4">CONCATENATE("", C3)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M3" s="39" t="str">
+      <c r="M3" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N3" s="39" t="str">
+      <c r="N3" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O3" s="39" t="str">
+      <c r="O3" s="38" t="str">
         <f t="shared" ref="O3:O22" si="5">F3</f>
         <v>SUS.Area</v>
       </c>
-      <c r="P3" s="39" t="s">
+      <c r="P3" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="Q3" s="39" t="s">
+      <c r="Q3" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="R3" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="S3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="39" t="str">
+      <c r="R3" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="S3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="38" t="str">
         <f t="shared" ref="T3:V21" si="6">SUBSTITUTE(D3, "_", " ")</f>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U3" s="39" t="str">
+      <c r="U3" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V3" s="39" t="str">
+      <c r="V3" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Area</v>
       </c>
-      <c r="W3" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X3" s="43" t="str">
+      <c r="W3" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X3" s="42" t="str">
         <f t="shared" ref="X3:X27" si="7">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
-      <c r="Y3" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z3" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB3" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="41" t="s">
+      <c r="Y3" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z3" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB3" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD3" s="40" t="s">
+      <c r="AD3" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="38">
+      <c r="A4" s="37">
         <v>4</v>
       </c>
-      <c r="B4" s="68" t="s">
-        <v>213</v>
+      <c r="B4" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C4" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="39" t="str">
+      <c r="G4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M4" s="39" t="str">
+      <c r="M4" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N4" s="39" t="str">
+      <c r="N4" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O4" s="39" t="str">
+      <c r="O4" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Box</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="P4" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="S4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="39" t="str">
+      <c r="R4" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="S4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U4" s="39" t="str">
+      <c r="U4" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V4" s="39" t="str">
+      <c r="V4" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Box</v>
       </c>
-      <c r="W4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X4" s="43" t="str">
+      <c r="W4" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X4" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-4</v>
       </c>
-      <c r="Y4" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="41" t="s">
+      <c r="Y4" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD4" s="40" t="s">
+      <c r="AD4" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="38">
+      <c r="A5" s="37">
         <v>5</v>
       </c>
-      <c r="B5" s="68" t="s">
-        <v>213</v>
+      <c r="B5" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="39" t="str">
+      <c r="G5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M5" s="39" t="str">
+      <c r="M5" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N5" s="39" t="str">
+      <c r="N5" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O5" s="39" t="str">
+      <c r="O5" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="P5" s="39" t="s">
+      <c r="P5" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="Q5" s="39" t="s">
+      <c r="Q5" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="R5" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="S5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="39" t="str">
+      <c r="R5" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="S5" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U5" s="39" t="str">
+      <c r="U5" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V5" s="39" t="str">
+      <c r="V5" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Consultório</v>
       </c>
-      <c r="W5" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X5" s="43" t="str">
+      <c r="W5" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X5" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-5</v>
       </c>
-      <c r="Y5" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="41" t="s">
+      <c r="Y5" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD5" s="40" t="s">
+      <c r="AD5" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
+      <c r="A6" s="37">
         <v>6</v>
       </c>
-      <c r="B6" s="68" t="s">
-        <v>213</v>
+      <c r="B6" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C6" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="39" t="str">
+      <c r="G6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M6" s="39" t="str">
+      <c r="M6" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N6" s="39" t="str">
+      <c r="N6" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O6" s="39" t="str">
+      <c r="O6" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="P6" s="39" t="s">
+      <c r="P6" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="Q6" s="39" t="s">
+      <c r="Q6" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="R6" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="S6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="39" t="str">
+      <c r="R6" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="S6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U6" s="39" t="str">
+      <c r="U6" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V6" s="39" t="str">
+      <c r="V6" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Enfermaria</v>
       </c>
-      <c r="W6" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X6" s="43" t="str">
+      <c r="W6" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X6" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-6</v>
       </c>
-      <c r="Y6" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="41" t="s">
+      <c r="Y6" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD6" s="40" t="s">
+      <c r="AD6" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="38">
+      <c r="A7" s="37">
         <v>7</v>
       </c>
-      <c r="B7" s="68" t="s">
-        <v>213</v>
+      <c r="B7" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C7" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="72" t="s">
+      <c r="E7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="39" t="str">
+      <c r="G7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M7" s="39" t="str">
+      <c r="M7" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N7" s="39" t="str">
+      <c r="N7" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O7" s="39" t="str">
+      <c r="O7" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="P7" s="39" t="s">
+      <c r="P7" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="Q7" s="39" t="s">
+      <c r="Q7" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="R7" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="S7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="39" t="str">
+      <c r="R7" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="S7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U7" s="39" t="str">
+      <c r="U7" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V7" s="39" t="str">
+      <c r="V7" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Laboratório</v>
       </c>
-      <c r="W7" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X7" s="43" t="str">
+      <c r="W7" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X7" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-7</v>
       </c>
-      <c r="Y7" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="41" t="s">
+      <c r="Y7" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD7" s="40" t="s">
+      <c r="AD7" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38">
+      <c r="A8" s="37">
         <v>8</v>
       </c>
-      <c r="B8" s="68" t="s">
-        <v>213</v>
+      <c r="B8" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="G8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="39" t="str">
+      <c r="G8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M8" s="39" t="str">
+      <c r="M8" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N8" s="39" t="str">
+      <c r="N8" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O8" s="39" t="str">
+      <c r="O8" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="P8" s="39" t="s">
+      <c r="P8" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="Q8" s="39" t="s">
+      <c r="Q8" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="R8" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="S8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="39" t="str">
+      <c r="R8" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="S8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U8" s="39" t="str">
+      <c r="U8" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V8" s="39" t="str">
+      <c r="V8" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Piscina</v>
       </c>
-      <c r="W8" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X8" s="43" t="str">
+      <c r="W8" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X8" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-8</v>
       </c>
-      <c r="Y8" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="41" t="s">
+      <c r="Y8" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD8" s="40" t="s">
+      <c r="AD8" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="38">
+      <c r="A9" s="37">
         <v>9</v>
       </c>
-      <c r="B9" s="68" t="s">
-        <v>213</v>
+      <c r="B9" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C9" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="E9" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="39" t="str">
+      <c r="G9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M9" s="39" t="str">
+      <c r="M9" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N9" s="39" t="str">
+      <c r="N9" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O9" s="39" t="str">
+      <c r="O9" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="P9" s="39" t="s">
+      <c r="P9" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="Q9" s="39" t="s">
+      <c r="Q9" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="R9" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="S9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="39" t="str">
+      <c r="R9" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="S9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U9" s="39" t="str">
+      <c r="U9" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V9" s="39" t="str">
+      <c r="V9" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Posto</v>
       </c>
-      <c r="W9" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X9" s="43" t="str">
+      <c r="W9" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X9" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-9</v>
       </c>
-      <c r="Y9" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="41" t="s">
+      <c r="Y9" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD9" s="40" t="s">
+      <c r="AD9" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38">
+      <c r="A10" s="37">
         <v>10</v>
       </c>
-      <c r="B10" s="68" t="s">
-        <v>213</v>
+      <c r="B10" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C10" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="G10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="39" t="str">
+      <c r="G10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M10" s="39" t="str">
+      <c r="M10" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N10" s="39" t="str">
+      <c r="N10" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O10" s="39" t="str">
+      <c r="O10" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="P10" s="39" t="s">
+      <c r="P10" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="Q10" s="39" t="s">
+      <c r="Q10" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="R10" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="S10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="39" t="str">
+      <c r="R10" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="S10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U10" s="39" t="str">
+      <c r="U10" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V10" s="39" t="str">
+      <c r="V10" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Quarto</v>
       </c>
-      <c r="W10" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X10" s="43" t="str">
+      <c r="W10" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X10" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-10</v>
       </c>
-      <c r="Y10" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="41" t="s">
+      <c r="Y10" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD10" s="40" t="s">
+      <c r="AD10" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="38">
+      <c r="A11" s="37">
         <v>11</v>
       </c>
-      <c r="B11" s="68" t="s">
-        <v>213</v>
+      <c r="B11" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C11" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="74" t="s">
+      <c r="F11" s="73" t="s">
         <v>121</v>
       </c>
-      <c r="G11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="39" t="str">
+      <c r="G11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M11" s="39" t="str">
+      <c r="M11" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N11" s="39" t="str">
+      <c r="N11" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="O11" s="39" t="str">
+      <c r="O11" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="P11" s="39" t="s">
+      <c r="P11" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="Q11" s="39" t="s">
+      <c r="Q11" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="R11" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="S11" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="39" t="str">
+      <c r="R11" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="S11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U11" s="39" t="str">
+      <c r="U11" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ambientes</v>
       </c>
-      <c r="V11" s="39" t="str">
+      <c r="V11" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Sala</v>
       </c>
-      <c r="W11" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X11" s="43" t="str">
+      <c r="W11" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X11" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-11</v>
       </c>
-      <c r="Y11" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="41" t="s">
+      <c r="Y11" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD11" s="40" t="s">
+      <c r="AD11" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="38">
+      <c r="A12" s="37">
         <v>12</v>
       </c>
-      <c r="B12" s="68" t="s">
-        <v>213</v>
+      <c r="B12" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="75" t="s">
+      <c r="F12" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="39" t="str">
+      <c r="G12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M12" s="39" t="str">
+      <c r="M12" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N12" s="39" t="str">
+      <c r="N12" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O12" s="39" t="str">
+      <c r="O12" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="P12" s="39" t="s">
+      <c r="P12" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="Q12" s="39" t="s">
+      <c r="Q12" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="R12" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="S12" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="39" t="str">
+      <c r="R12" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="S12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U12" s="39" t="str">
+      <c r="U12" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V12" s="39" t="str">
+      <c r="V12" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Zoneamento</v>
       </c>
-      <c r="W12" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X12" s="43" t="str">
+      <c r="W12" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X12" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-12</v>
       </c>
-      <c r="Y12" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="41" t="s">
+      <c r="Y12" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="AD12" s="40" t="s">
+      <c r="AD12" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="38">
+      <c r="A13" s="37">
         <v>13</v>
       </c>
-      <c r="B13" s="68" t="s">
-        <v>213</v>
+      <c r="B13" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C13" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="72" t="s">
+      <c r="E13" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="39" t="str">
+      <c r="G13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M13" s="39" t="str">
+      <c r="M13" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N13" s="39" t="str">
+      <c r="N13" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O13" s="39" t="str">
+      <c r="O13" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="P13" s="39" t="s">
+      <c r="P13" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="Q13" s="39" t="s">
+      <c r="Q13" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="R13" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="S13" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="39" t="str">
+      <c r="R13" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="S13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U13" s="39" t="str">
+      <c r="U13" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V13" s="39" t="str">
+      <c r="V13" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Unidade.Funcional</v>
       </c>
-      <c r="W13" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X13" s="43" t="str">
+      <c r="W13" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X13" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-13</v>
       </c>
-      <c r="Y13" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="41" t="s">
+      <c r="Y13" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z13" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB13" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="AD13" s="40" t="s">
+      <c r="AD13" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="38">
+      <c r="A14" s="37">
         <v>14</v>
       </c>
-      <c r="B14" s="68" t="s">
-        <v>213</v>
+      <c r="B14" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C14" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="72" t="s">
+      <c r="E14" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="39" t="str">
+      <c r="G14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M14" s="39" t="str">
+      <c r="M14" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="N14" s="39" t="str">
+      <c r="N14" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="O14" s="39" t="str">
+      <c r="O14" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="P14" s="39" t="s">
+      <c r="P14" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="Q14" s="39" t="s">
+      <c r="Q14" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="R14" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="S14" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="39" t="str">
+      <c r="R14" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="S14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Ocupação</v>
       </c>
-      <c r="U14" s="39" t="str">
+      <c r="U14" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Funcional</v>
       </c>
-      <c r="V14" s="39" t="str">
+      <c r="V14" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Setor</v>
       </c>
-      <c r="W14" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X14" s="43" t="str">
+      <c r="W14" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X14" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-14</v>
       </c>
-      <c r="Y14" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="41" t="s">
+      <c r="Y14" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="AD14" s="40" t="s">
+      <c r="AD14" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="38">
+      <c r="A15" s="37">
         <v>15</v>
       </c>
-      <c r="B15" s="68" t="s">
-        <v>213</v>
+      <c r="B15" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C15" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="E15" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="39" t="str">
+      <c r="G15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M15" s="39" t="str">
+      <c r="M15" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N15" s="39" t="str">
+      <c r="N15" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O15" s="39" t="str">
+      <c r="O15" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="P15" s="39" t="s">
+      <c r="P15" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="Q15" s="39" t="s">
+      <c r="Q15" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="R15" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="S15" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T15" s="39" t="str">
+      <c r="R15" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="S15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U15" s="39" t="str">
+      <c r="U15" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V15" s="39" t="str">
+      <c r="V15" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Robot</v>
       </c>
-      <c r="W15" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X15" s="43" t="str">
+      <c r="W15" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X15" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-15</v>
       </c>
-      <c r="Y15" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="40" t="s">
+      <c r="Y15" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z15" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AB15" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="41" t="s">
+      <c r="AB15" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD15" s="40" t="s">
+      <c r="AD15" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="38">
+      <c r="A16" s="37">
         <v>16</v>
       </c>
-      <c r="B16" s="68" t="s">
-        <v>213</v>
+      <c r="B16" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="72" t="s">
+      <c r="E16" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="F16" s="75" t="s">
+      <c r="F16" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="39" t="str">
+      <c r="G16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M16" s="39" t="str">
+      <c r="M16" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N16" s="39" t="str">
+      <c r="N16" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O16" s="39" t="str">
+      <c r="O16" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="P16" s="39" t="s">
+      <c r="P16" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="Q16" s="39" t="s">
+      <c r="Q16" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="R16" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="S16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T16" s="39" t="str">
+      <c r="R16" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="S16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U16" s="39" t="str">
+      <c r="U16" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V16" s="39" t="str">
+      <c r="V16" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamento</v>
       </c>
-      <c r="W16" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X16" s="43" t="str">
+      <c r="W16" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X16" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-16</v>
       </c>
-      <c r="Y16" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="40" t="s">
+      <c r="Y16" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AB16" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="41" t="s">
+      <c r="AB16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD16" s="40" t="s">
+      <c r="AD16" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38">
+      <c r="A17" s="37">
         <v>17</v>
       </c>
-      <c r="B17" s="68" t="s">
-        <v>213</v>
+      <c r="B17" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C17" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="72" t="s">
+      <c r="D17" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="39" t="str">
+      <c r="G17" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M17" s="39" t="str">
+      <c r="M17" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N17" s="39" t="str">
+      <c r="N17" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O17" s="39" t="str">
+      <c r="O17" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="P17" s="39" t="s">
+      <c r="P17" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="Q17" s="39" t="s">
+      <c r="Q17" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="R17" s="40" t="s">
-        <v>235</v>
-      </c>
-      <c r="S17" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T17" s="39" t="str">
+      <c r="R17" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="S17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U17" s="39" t="str">
+      <c r="U17" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V17" s="39" t="str">
+      <c r="V17" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Dispositivo</v>
       </c>
-      <c r="W17" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X17" s="43" t="str">
+      <c r="W17" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X17" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-17</v>
       </c>
-      <c r="Y17" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="40" t="s">
+      <c r="Y17" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AB17" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="41" t="s">
+      <c r="AB17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD17" s="40" t="s">
+      <c r="AD17" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="38">
+      <c r="A18" s="37">
         <v>18</v>
       </c>
-      <c r="B18" s="68" t="s">
-        <v>213</v>
+      <c r="B18" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C18" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="D18" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="75" t="s">
+      <c r="F18" s="74" t="s">
         <v>142</v>
       </c>
-      <c r="G18" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="39" t="str">
+      <c r="G18" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M18" s="39" t="str">
+      <c r="M18" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N18" s="39" t="str">
+      <c r="N18" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O18" s="39" t="str">
+      <c r="O18" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="P18" s="39" t="s">
+      <c r="P18" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="Q18" s="39" t="s">
+      <c r="Q18" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="R18" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="S18" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T18" s="39" t="str">
+      <c r="R18" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="S18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U18" s="39" t="str">
+      <c r="U18" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V18" s="39" t="str">
+      <c r="V18" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Instrumento</v>
       </c>
-      <c r="W18" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X18" s="43" t="str">
+      <c r="W18" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X18" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-18</v>
       </c>
-      <c r="Y18" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="40" t="s">
+      <c r="Y18" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="AB18" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="41" t="s">
+      <c r="AB18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD18" s="40" t="s">
+      <c r="AD18" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38">
+      <c r="A19" s="37">
         <v>19</v>
       </c>
-      <c r="B19" s="68" t="s">
-        <v>213</v>
+      <c r="B19" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C19" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="39" t="str">
+      <c r="G19" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M19" s="39" t="str">
+      <c r="M19" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N19" s="39" t="str">
+      <c r="N19" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="O19" s="39" t="str">
+      <c r="O19" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="P19" s="39" t="s">
+      <c r="P19" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="Q19" s="39" t="s">
+      <c r="Q19" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="R19" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="S19" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T19" s="39" t="str">
+      <c r="R19" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="S19" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U19" s="39" t="str">
+      <c r="U19" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Equipamentos</v>
       </c>
-      <c r="V19" s="39" t="str">
+      <c r="V19" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília.de.Saúde</v>
       </c>
-      <c r="W19" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X19" s="43" t="str">
+      <c r="W19" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X19" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-19</v>
       </c>
-      <c r="Y19" s="40" t="s">
+      <c r="Y19" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="Z19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="40" t="s">
+      <c r="Z19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="AB19" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="41" t="s">
+      <c r="AB19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD19" s="40" t="s">
+      <c r="AD19" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38">
+      <c r="A20" s="37">
         <v>20</v>
       </c>
-      <c r="B20" s="68" t="s">
-        <v>213</v>
+      <c r="B20" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C20" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="72" t="s">
+      <c r="E20" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="39" t="str">
+      <c r="G20" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M20" s="39" t="str">
+      <c r="M20" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N20" s="39" t="str">
+      <c r="N20" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O20" s="39" t="str">
+      <c r="O20" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="P20" s="39" t="s">
+      <c r="P20" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="Q20" s="39" t="s">
+      <c r="Q20" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="R20" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="S20" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T20" s="39" t="str">
+      <c r="R20" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="S20" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U20" s="39" t="str">
+      <c r="U20" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V20" s="39" t="str">
+      <c r="V20" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Mobília</v>
       </c>
-      <c r="W20" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X20" s="43" t="str">
+      <c r="W20" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X20" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-20</v>
       </c>
-      <c r="Y20" s="40" t="s">
+      <c r="Y20" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="Z20" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="40" t="s">
+      <c r="Z20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="AB20" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="41" t="s">
+      <c r="AB20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD20" s="40" t="s">
+      <c r="AD20" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="38">
+      <c r="A21" s="37">
         <v>21</v>
       </c>
-      <c r="B21" s="68" t="s">
-        <v>213</v>
+      <c r="B21" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C21" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="72" t="s">
+      <c r="E21" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="75" t="s">
+      <c r="F21" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="G21" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="39" t="str">
+      <c r="G21" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SomaSUS</v>
       </c>
-      <c r="M21" s="39" t="str">
+      <c r="M21" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N21" s="39" t="str">
+      <c r="N21" s="38" t="str">
         <f t="shared" si="4"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O21" s="39" t="str">
+      <c r="O21" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="P21" s="39" t="s">
+      <c r="P21" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="Q21" s="39" t="s">
+      <c r="Q21" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="R21" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="S21" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T21" s="39" t="str">
+      <c r="R21" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="S21" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U21" s="39" t="str">
+      <c r="U21" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V21" s="39" t="str">
+      <c r="V21" s="38" t="str">
         <f t="shared" si="6"/>
         <v>SUS.Roupa</v>
       </c>
-      <c r="W21" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X21" s="43" t="str">
+      <c r="W21" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X21" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-21</v>
       </c>
-      <c r="Y21" s="40" t="s">
+      <c r="Y21" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="Z21" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="40" t="s">
+      <c r="Z21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="AB21" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="41" t="s">
+      <c r="AB21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD21" s="40" t="s">
+      <c r="AD21" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38">
+      <c r="A22" s="37">
         <v>22</v>
       </c>
-      <c r="B22" s="68" t="s">
-        <v>213</v>
+      <c r="B22" s="65" t="s">
+        <v>199</v>
       </c>
       <c r="C22" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="72" t="s">
+      <c r="D22" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="72" t="s">
+      <c r="E22" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="F22" s="75" t="s">
+      <c r="F22" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L22" s="39" t="str">
-        <f t="shared" ref="L22:N22" si="8">CONCATENATE("", C22)</f>
+      <c r="G22" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="38" t="str">
+        <f t="shared" ref="L22:N27" si="8">CONCATENATE("", C22)</f>
         <v>SomaSUS</v>
       </c>
-      <c r="M22" s="39" t="str">
+      <c r="M22" s="38" t="str">
         <f t="shared" si="8"/>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="N22" s="39" t="str">
+      <c r="N22" s="38" t="str">
         <f t="shared" si="8"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="O22" s="39" t="str">
+      <c r="O22" s="38" t="str">
         <f t="shared" si="5"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="P22" s="39" t="s">
+      <c r="P22" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="Q22" s="39" t="s">
+      <c r="Q22" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="R22" s="40" t="s">
-        <v>239</v>
-      </c>
-      <c r="S22" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="T22" s="39" t="str">
+      <c r="R22" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="S22" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="38" t="str">
         <f t="shared" ref="T22:V22" si="9">SUBSTITUTE(D22, "_", " ")</f>
         <v>SUS.Assistência.Médica</v>
       </c>
-      <c r="U22" s="39" t="str">
+      <c r="U22" s="38" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Hotelaria</v>
       </c>
-      <c r="V22" s="39" t="str">
+      <c r="V22" s="38" t="str">
         <f t="shared" si="9"/>
         <v>SUS.Alimentação</v>
       </c>
-      <c r="W22" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X22" s="43" t="str">
+      <c r="W22" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X22" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-22</v>
       </c>
-      <c r="Y22" s="40" t="s">
+      <c r="Y22" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="Z22" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="40" t="s">
+      <c r="Z22" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="AB22" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="41" t="s">
+      <c r="AB22" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="AD22" s="40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="38">
+      <c r="AD22" s="39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37">
         <v>23</v>
       </c>
-      <c r="B23" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="C23" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="E23" s="70" t="s">
-        <v>246</v>
-      </c>
-      <c r="F23" s="70" t="s">
-        <v>271</v>
-      </c>
-      <c r="G23" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="39" t="str">
-        <f t="shared" ref="L23:O27" si="10">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M23" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="N23" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O23" s="39" t="str">
+      <c r="B23" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="E23" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="F23" s="66" t="s">
+        <v>253</v>
+      </c>
+      <c r="G23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M23" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N23" s="38" t="str">
+        <f t="shared" ref="N23:O27" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E23),"."," ")," De "," de "))</f>
+        <v>API Método</v>
+      </c>
+      <c r="O23" s="38" t="str">
         <f t="shared" si="10"/>
         <v>Função Auxiliar</v>
       </c>
-      <c r="P23" s="40" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q23" s="40" t="s">
-        <v>273</v>
-      </c>
-      <c r="R23" s="40" t="s">
-        <v>274</v>
-      </c>
-      <c r="S23" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="T23" s="40" t="str">
+      <c r="P23" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q23" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="R23" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="S23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="39" t="str">
         <f t="shared" ref="T23:V27" si="11">SUBSTITUTE(C23, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U23" s="40" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U23" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="V23" s="41" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V23" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W23" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X23" s="43" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="W23" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X23" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-23</v>
       </c>
-      <c r="Y23" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD23" s="40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="38">
+      <c r="Y23" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="37">
         <v>24</v>
       </c>
-      <c r="B24" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="E24" s="70" t="s">
-        <v>246</v>
-      </c>
-      <c r="F24" s="70" t="s">
+      <c r="B24" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="C24" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="G24" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="39" t="str">
+      <c r="D24" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="E24" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" s="66" t="s">
+        <v>257</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M24" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N24" s="38" t="str">
         <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="M24" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="N24" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O24" s="39" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="O24" s="38" t="str">
         <f t="shared" si="10"/>
         <v>Função Global</v>
       </c>
-      <c r="P24" s="40" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q24" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="R24" s="40" t="s">
-        <v>278</v>
-      </c>
-      <c r="S24" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="T24" s="40" t="str">
+      <c r="P24" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q24" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="R24" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="S24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="U24" s="40" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U24" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="V24" s="41" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V24" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W24" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X24" s="43" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="W24" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X24" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-24</v>
       </c>
-      <c r="Y24" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="38">
+      <c r="Y24" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="37">
         <v>25</v>
       </c>
-      <c r="B25" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="D25" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="E25" s="70" t="s">
-        <v>246</v>
-      </c>
-      <c r="F25" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="G25" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="39" t="str">
+      <c r="B25" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="F25" s="66" t="s">
+        <v>261</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M25" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N25" s="38" t="str">
         <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="M25" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="N25" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O25" s="39" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="O25" s="38" t="str">
         <f t="shared" si="10"/>
         <v>Função Local</v>
       </c>
-      <c r="P25" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q25" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="R25" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="S25" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="T25" s="40" t="str">
+      <c r="P25" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q25" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="R25" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="S25" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="U25" s="40" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U25" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="V25" s="41" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V25" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W25" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X25" s="43" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="W25" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X25" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-25</v>
       </c>
-      <c r="Y25" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="38">
+      <c r="Y25" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37">
         <v>26</v>
       </c>
-      <c r="B26" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="D26" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="E26" s="70" t="s">
-        <v>246</v>
-      </c>
-      <c r="F26" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="G26" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="39" t="str">
+      <c r="B26" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="E26" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>265</v>
+      </c>
+      <c r="G26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M26" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N26" s="38" t="str">
         <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="M26" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="N26" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O26" s="39" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="O26" s="38" t="str">
         <f t="shared" si="10"/>
         <v>Função Filtro</v>
       </c>
-      <c r="P26" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q26" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="R26" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="S26" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="T26" s="40" t="str">
+      <c r="P26" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q26" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="R26" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="S26" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T26" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="U26" s="40" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U26" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="V26" s="41" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V26" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W26" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X26" s="43" t="str">
+        <v>API Método</v>
+      </c>
+      <c r="W26" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X26" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-26</v>
       </c>
-      <c r="Y26" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD26" s="40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="38">
+      <c r="Y26" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="37">
         <v>27</v>
       </c>
-      <c r="B27" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="C27" s="70" t="s">
-        <v>245</v>
-      </c>
-      <c r="D27" s="70" t="s">
-        <v>247</v>
-      </c>
-      <c r="E27" s="70" t="s">
-        <v>287</v>
-      </c>
-      <c r="F27" s="70" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K27" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L27" s="39" t="str">
+      <c r="B27" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="D27" s="66" t="s">
+        <v>278</v>
+      </c>
+      <c r="E27" s="66" t="s">
+        <v>279</v>
+      </c>
+      <c r="F27" s="66" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M27" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>API.Macros.Visuais</v>
+      </c>
+      <c r="N27" s="38" t="str">
         <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="M27" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="N27" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O27" s="39" t="str">
+        <v>API Método Visual</v>
+      </c>
+      <c r="O27" s="38" t="str">
         <f t="shared" si="10"/>
         <v>Bloco de Código</v>
       </c>
-      <c r="P27" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q27" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="R27" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S27" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="T27" s="40" t="str">
+      <c r="P27" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q27" s="39" t="s">
+        <v>271</v>
+      </c>
+      <c r="R27" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="S27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>De API</v>
-      </c>
-      <c r="U27" s="40" t="str">
+        <v>API Plataforma</v>
+      </c>
+      <c r="U27" s="39" t="str">
         <f t="shared" si="11"/>
-        <v>Macros</v>
-      </c>
-      <c r="V27" s="41" t="str">
+        <v>API Macros Visuais</v>
+      </c>
+      <c r="V27" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="W27" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X27" s="43" t="str">
+        <v>API Método Visual</v>
+      </c>
+      <c r="W27" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="X27" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-27</v>
       </c>
-      <c r="Y27" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="40" t="s">
+      <c r="Y27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="50" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B27">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+  <conditionalFormatting sqref="A23:A27">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B22">
+    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="30" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27:F27">
-    <cfRule type="duplicateValues" dxfId="29" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="28" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F26">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+  <conditionalFormatting sqref="F23:F27">
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R22">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:W22 W23:W27">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
+  <conditionalFormatting sqref="T2:W22">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W23:W27">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC22 AE2:XFD22 Y3:Y22 AA3:AA22">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5402,72 +5617,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="T1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="U1" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="29">
+      <c r="A2" s="28">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -5598,17 +5813,17 @@
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="32" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="31" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="31" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="22" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.42578125" style="22" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="32" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="31" customWidth="1"/>
     <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="3.7109375" style="63" customWidth="1"/>
+    <col min="14" max="23" width="3.7109375" style="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5651,34 +5866,34 @@
       <c r="M1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="64" t="s">
+      <c r="N1" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="64" t="s">
+      <c r="O1" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="P1" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="64" t="s">
+      <c r="Q1" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="64" t="s">
+      <c r="R1" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="64" t="s">
+      <c r="S1" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="64" t="s">
+      <c r="T1" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="U1" s="64" t="s">
+      <c r="U1" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="V1" s="64" t="s">
+      <c r="V1" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="64" t="s">
+      <c r="W1" s="59" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5689,67 +5904,67 @@
       <c r="B2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="H2" s="35" t="s">
+      <c r="F2" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H2" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="L2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="66" t="s">
+      <c r="L2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="61" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5760,67 +5975,67 @@
       <c r="B3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="F3" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="H3" s="35" t="s">
+      <c r="F3" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="L3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W3" s="66" t="s">
+      <c r="L3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="61" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5831,67 +6046,67 @@
       <c r="B4" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G4" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="H4" s="35" t="s">
+      <c r="F4" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="K4" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="L4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P4" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="66" t="s">
+      <c r="L4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="61" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5902,427 +6117,427 @@
       <c r="B5" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G5" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="H5" s="35" t="s">
+      <c r="F5" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H5" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="L5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L5" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="23">
         <v>6</v>
       </c>
-      <c r="B6" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D6" s="59" t="s">
+      <c r="B6" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="H6" s="35" t="s">
+      <c r="E6" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I6" s="60" t="s">
-        <v>252</v>
-      </c>
-      <c r="J6" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="61" t="str">
+      <c r="I6" s="55" t="s">
+        <v>234</v>
+      </c>
+      <c r="J6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="56" t="str">
         <f t="shared" ref="L6:L10" si="0">IF(M6="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="M6" s="62" t="s">
-        <v>253</v>
-      </c>
-      <c r="N6" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M6" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="N6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="23">
         <v>7</v>
       </c>
-      <c r="B7" s="58" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G7" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="H7" s="35" t="s">
+      <c r="E7" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="H7" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="60" t="s">
-        <v>256</v>
-      </c>
-      <c r="J7" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="61" t="str">
+      <c r="I7" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="J7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="56" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M7" s="62" t="s">
-        <v>257</v>
-      </c>
-      <c r="N7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M7" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="N7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23">
         <v>8</v>
       </c>
-      <c r="B8" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D8" s="59" t="s">
+      <c r="B8" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G8" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="H8" s="35" t="s">
+      <c r="E8" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="H8" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="J8" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="61" t="str">
+      <c r="I8" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="J8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="56" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M8" s="62" t="s">
-        <v>261</v>
-      </c>
-      <c r="N8" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="N8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="23">
         <v>9</v>
       </c>
-      <c r="B9" s="58" t="s">
-        <v>262</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D9" s="59" t="s">
+      <c r="B9" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="G9" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="H9" s="35" t="s">
+      <c r="E9" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="J9" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="61" t="str">
+      <c r="I9" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="56" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M9" s="62" t="s">
-        <v>265</v>
-      </c>
-      <c r="N9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M9" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="N9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23">
         <v>10</v>
       </c>
-      <c r="B10" s="58" t="s">
-        <v>266</v>
-      </c>
-      <c r="C10" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" s="59" t="s">
+      <c r="B10" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="H10" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="55" t="s">
         <v>250</v>
       </c>
-      <c r="G10" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="60" t="s">
-        <v>268</v>
-      </c>
-      <c r="J10" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="61" t="str">
+      <c r="J10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="56" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="M10" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="N10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="66" t="s">
+      <c r="M10" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="N10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="61" t="s">
         <v>1</v>
       </c>
     </row>

--- a/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E3B8CD-94FA-491E-9A2B-FD1741527234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7855A940-0702-4C3E-B843-564CE401F347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="30" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="310">
   <si>
     <t>Key</t>
   </si>
@@ -259,30 +259,9 @@
     <t>Escola Politécnica da UFRJ</t>
   </si>
   <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -328,9 +307,6 @@
     <t>VOL.04</t>
   </si>
   <si>
-    <t>Volumes do Caderno SUS</t>
-  </si>
-  <si>
     <t>tema</t>
   </si>
   <si>
@@ -583,9 +559,6 @@
     <t>en</t>
   </si>
   <si>
-    <t>Caderno SomaSUS elaborado pelo Sistema Único de Saúde do Brasil</t>
-  </si>
-  <si>
     <t>Aviso</t>
   </si>
   <si>
@@ -922,100 +895,121 @@
     <t>API.Método.Visual</t>
   </si>
   <si>
-    <t>Fonte.Brasil.01</t>
-  </si>
-  <si>
-    <t>Fonte.Brasil.02</t>
-  </si>
-  <si>
-    <t>Fonte.Brasil.03</t>
-  </si>
-  <si>
-    <t>Fonte.Brasil.04</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.01</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.02</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.03</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.04</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.05</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.06</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.07</t>
-  </si>
-  <si>
-    <t>Fonte.Vegetação.08</t>
-  </si>
-  <si>
-    <t>Fonte.SINAPI</t>
-  </si>
-  <si>
-    <t>Fonte.Brasil.Saúde.01</t>
-  </si>
-  <si>
-    <t>Fonte.Brasil.Saúde.02</t>
-  </si>
-  <si>
     <t>https://anvisalegis.datalegis.net</t>
   </si>
   <si>
-    <t>Fonte.Brasil.Saúde.03</t>
-  </si>
-  <si>
     <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
   </si>
   <si>
-    <t>Fonte.Brasil.Saúde.04</t>
-  </si>
-  <si>
     <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
   </si>
   <si>
-    <t>Fonte.NBR.01</t>
-  </si>
-  <si>
     <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
   </si>
   <si>
-    <t>Fonte.NBR.02</t>
-  </si>
-  <si>
     <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
   </si>
   <si>
-    <t>Fonte.NBR.03</t>
-  </si>
-  <si>
     <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
   </si>
   <si>
-    <t>Fonte.NBR.04</t>
-  </si>
-  <si>
     <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
   </si>
   <si>
-    <t>Fonte.NBR.05</t>
-  </si>
-  <si>
     <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
   </si>
   <si>
-    <t>Fonte.Bombeiros.01</t>
-  </si>
-  <si>
-    <t>IT Bombeiros (estadual). Segurança contra incêndio. Varia por estado — consultar VISA local.</t>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1114,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1313,6 +1307,12 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1366,7 +1366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1610,6 +1610,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2239,59 +2245,60 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3893FB0-44DC-47E8-B3E0-611685D282EA}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="85" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" s="81" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="84" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>48</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
         <v>52</v>
       </c>
       <c r="B5" s="14" t="str">
@@ -2299,11 +2306,11 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
         <v>53</v>
       </c>
       <c r="B6" s="14" t="str">
@@ -2311,495 +2318,493 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="C17" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46274.303017129627</v>
+        <v>46276.461855787034</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>70</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>160</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>167</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="17" t="str">
-        <f>_xlfn.TRANSLATE(B21,"pt","es")</f>
-        <v>Cuaderno SomaSUS preparado por el Sistema Unificado de Salud de Brasil</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="B23" s="17" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
-        <v>Cuaderno SomaSUS prepared by the Unified Health System of Brazil</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>161</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize the SomaSUS Notebook prepared by the Unified Health System of Brazil.</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="77" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B27" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="77" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="77" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="77" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="78" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B32" s="78" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B33" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="79" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B35" s="79" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B36" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B37" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="C27" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="45" t="s">
+      <c r="C37" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="43" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B38" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="77" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B31" s="78" t="s">
+      <c r="C38" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="80" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="C31" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="B32" s="78" t="s">
+      <c r="C39" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B40" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="B33" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B34" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B35" s="79" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B36" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B37" s="79" t="s">
-        <v>194</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="B38" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="80" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B39" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="B40" s="47" t="s">
-        <v>198</v>
-      </c>
       <c r="C40" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B41" s="82" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B42" s="83" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B43" s="83" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B44" s="83" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B45" s="83" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B46" s="83" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>306</v>
       </c>
       <c r="B47" s="83" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C47" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="B48" s="83" t="s">
+        <v>278</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="81" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B48" s="83" t="s">
+      <c r="B49" s="83" t="s">
         <v>309</v>
       </c>
-      <c r="C48" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" s="81" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B49" s="83" t="s">
-        <v>311</v>
-      </c>
       <c r="C49" s="33" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B27" r:id="rId1" xr:uid="{88DD90D0-931F-4AAC-AE7E-516F82689E7D}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{645F0605-0703-420A-BEE4-A645E90ACDFC}"/>
-    <hyperlink ref="B28" r:id="rId3" xr:uid="{B08EA68F-728E-4768-B845-95C20330440C}"/>
-    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{D4029F2D-4B86-4D86-9A84-0D744B69DFE3}"/>
-    <hyperlink ref="B40" r:id="rId5" xr:uid="{71DCF592-0061-42CE-9049-9B3CB669E301}"/>
-    <hyperlink ref="B41" r:id="rId6" xr:uid="{32BAD505-06E3-40A9-A25F-6A2E6C77E9CE}"/>
-    <hyperlink ref="B30" r:id="rId7" xr:uid="{D24CD502-BC2F-4045-AE05-736D65D9F826}"/>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{EA358FBA-C868-49DA-B303-7D605016EF68}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{9FE14064-2FB3-48CA-A688-EFB768757227}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{CD18A09A-A5E4-4CC7-82B7-B32F063F711C}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{37643CEE-BBF8-4251-A510-1ED02D0D4365}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{5496497F-DBD5-4EE0-BD67-DAB2CB6BF85F}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{5CAAC6DE-DA30-4807-B2E5-FA9BFDB1CEFF}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{AF645B89-E476-47A9-9202-5D630CB2388C}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2893,10 +2898,10 @@
         <v>41</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="S1" s="75" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="T1" s="27" t="s">
         <v>42</v>
@@ -2914,22 +2919,22 @@
         <v>0</v>
       </c>
       <c r="Y1" s="27" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="Z1" s="27" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AC1" s="27" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AD1" s="27" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -2937,19 +2942,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C2" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F2" s="70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G2" s="52" t="s">
         <v>1</v>
@@ -2983,13 +2988,13 @@
         <v>SUS.Volume</v>
       </c>
       <c r="P2" s="38" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="Q2" s="38" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="S2" s="67" t="s">
         <v>1</v>
@@ -3007,26 +3012,26 @@
         <v>SUS.Volume</v>
       </c>
       <c r="W2" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X2" s="42" t="str">
         <f t="shared" ref="X2" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
       <c r="Y2" s="48" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="Z2" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA2" s="49" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="AB2" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC2" s="40" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AD2" s="39" t="s">
         <v>1</v>
@@ -3037,19 +3042,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C3" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F3" s="72" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G3" s="52" t="s">
         <v>1</v>
@@ -3083,13 +3088,13 @@
         <v>SUS.Area</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="Q3" s="38" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="R3" s="39" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="S3" s="67" t="s">
         <v>1</v>
@@ -3107,26 +3112,26 @@
         <v>SUS.Area</v>
       </c>
       <c r="W3" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X3" s="42" t="str">
         <f t="shared" ref="X3:X27" si="7">CONCATENATE("Key-SUS-",A3)</f>
         <v>Key-SUS-3</v>
       </c>
       <c r="Y3" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z3" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA3" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB3" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC3" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD3" s="39" t="s">
         <v>1</v>
@@ -3137,19 +3142,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C4" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F4" s="72" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G4" s="52" t="s">
         <v>1</v>
@@ -3183,13 +3188,13 @@
         <v>SUS.Box</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="Q4" s="38" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="S4" s="67" t="s">
         <v>1</v>
@@ -3207,26 +3212,26 @@
         <v>SUS.Box</v>
       </c>
       <c r="W4" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X4" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-4</v>
       </c>
       <c r="Y4" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z4" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA4" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB4" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC4" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD4" s="39" t="s">
         <v>1</v>
@@ -3237,19 +3242,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C5" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E5" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F5" s="72" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G5" s="52" t="s">
         <v>1</v>
@@ -3283,13 +3288,13 @@
         <v>SUS.Consultório</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="Q5" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>1</v>
@@ -3307,26 +3312,26 @@
         <v>SUS.Consultório</v>
       </c>
       <c r="W5" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X5" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-5</v>
       </c>
       <c r="Y5" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z5" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA5" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB5" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC5" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD5" s="39" t="s">
         <v>1</v>
@@ -3337,19 +3342,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C6" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F6" s="72" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G6" s="52" t="s">
         <v>1</v>
@@ -3383,13 +3388,13 @@
         <v>SUS.Enfermaria</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Q6" s="38" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="R6" s="39" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="S6" s="67" t="s">
         <v>1</v>
@@ -3407,26 +3412,26 @@
         <v>SUS.Enfermaria</v>
       </c>
       <c r="W6" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X6" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-6</v>
       </c>
       <c r="Y6" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z6" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA6" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB6" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC6" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD6" s="39" t="s">
         <v>1</v>
@@ -3437,19 +3442,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C7" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E7" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F7" s="72" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G7" s="52" t="s">
         <v>1</v>
@@ -3483,13 +3488,13 @@
         <v>SUS.Laboratório</v>
       </c>
       <c r="P7" s="38" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="Q7" s="38" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="S7" s="67" t="s">
         <v>1</v>
@@ -3507,26 +3512,26 @@
         <v>SUS.Laboratório</v>
       </c>
       <c r="W7" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X7" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-7</v>
       </c>
       <c r="Y7" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z7" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA7" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB7" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC7" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD7" s="39" t="s">
         <v>1</v>
@@ -3537,19 +3542,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C8" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E8" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G8" s="52" t="s">
         <v>1</v>
@@ -3583,13 +3588,13 @@
         <v>SUS.Piscina</v>
       </c>
       <c r="P8" s="38" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="Q8" s="38" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="R8" s="39" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="S8" s="67" t="s">
         <v>1</v>
@@ -3607,26 +3612,26 @@
         <v>SUS.Piscina</v>
       </c>
       <c r="W8" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X8" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-8</v>
       </c>
       <c r="Y8" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z8" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA8" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB8" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC8" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD8" s="39" t="s">
         <v>1</v>
@@ -3637,19 +3642,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C9" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E9" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F9" s="72" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G9" s="52" t="s">
         <v>1</v>
@@ -3683,13 +3688,13 @@
         <v>SUS.Posto</v>
       </c>
       <c r="P9" s="38" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="Q9" s="38" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="R9" s="39" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="S9" s="67" t="s">
         <v>1</v>
@@ -3707,26 +3712,26 @@
         <v>SUS.Posto</v>
       </c>
       <c r="W9" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X9" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-9</v>
       </c>
       <c r="Y9" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z9" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA9" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB9" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC9" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD9" s="39" t="s">
         <v>1</v>
@@ -3737,19 +3742,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C10" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F10" s="72" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G10" s="52" t="s">
         <v>1</v>
@@ -3783,13 +3788,13 @@
         <v>SUS.Quarto</v>
       </c>
       <c r="P10" s="38" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q10" s="38" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="R10" s="39" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="S10" s="67" t="s">
         <v>1</v>
@@ -3807,26 +3812,26 @@
         <v>SUS.Quarto</v>
       </c>
       <c r="W10" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X10" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-10</v>
       </c>
       <c r="Y10" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z10" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA10" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB10" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC10" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD10" s="39" t="s">
         <v>1</v>
@@ -3837,19 +3842,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C11" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E11" s="71" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F11" s="73" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G11" s="52" t="s">
         <v>1</v>
@@ -3883,13 +3888,13 @@
         <v>SUS.Sala</v>
       </c>
       <c r="P11" s="38" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="Q11" s="38" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="R11" s="39" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="S11" s="67" t="s">
         <v>1</v>
@@ -3907,26 +3912,26 @@
         <v>SUS.Sala</v>
       </c>
       <c r="W11" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X11" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-11</v>
       </c>
       <c r="Y11" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z11" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA11" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB11" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC11" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD11" s="39" t="s">
         <v>1</v>
@@ -3937,19 +3942,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F12" s="74" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G12" s="52" t="s">
         <v>1</v>
@@ -3983,13 +3988,13 @@
         <v>SUS.Zoneamento</v>
       </c>
       <c r="P12" s="38" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="Q12" s="38" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="R12" s="39" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="S12" s="67" t="s">
         <v>1</v>
@@ -4007,26 +4012,26 @@
         <v>SUS.Zoneamento</v>
       </c>
       <c r="W12" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X12" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-12</v>
       </c>
       <c r="Y12" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z12" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA12" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB12" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC12" s="40" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AD12" s="39" t="s">
         <v>1</v>
@@ -4037,19 +4042,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C13" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E13" s="71" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G13" s="52" t="s">
         <v>1</v>
@@ -4083,13 +4088,13 @@
         <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="P13" s="38" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q13" s="38" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="R13" s="39" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="S13" s="67" t="s">
         <v>1</v>
@@ -4107,26 +4112,26 @@
         <v>SUS.Unidade.Funcional</v>
       </c>
       <c r="W13" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X13" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-13</v>
       </c>
       <c r="Y13" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z13" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA13" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB13" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC13" s="40" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="AD13" s="39" t="s">
         <v>1</v>
@@ -4137,19 +4142,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C14" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E14" s="71" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F14" s="74" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G14" s="52" t="s">
         <v>1</v>
@@ -4183,13 +4188,13 @@
         <v>SUS.Setor</v>
       </c>
       <c r="P14" s="38" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="Q14" s="38" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="R14" s="39" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="S14" s="67" t="s">
         <v>1</v>
@@ -4207,26 +4212,26 @@
         <v>SUS.Setor</v>
       </c>
       <c r="W14" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X14" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-14</v>
       </c>
       <c r="Y14" s="39" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Z14" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA14" s="39" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AB14" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC14" s="40" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="AD14" s="39" t="s">
         <v>1</v>
@@ -4237,19 +4242,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C15" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G15" s="52" t="s">
         <v>1</v>
@@ -4283,13 +4288,13 @@
         <v>SUS.Robot</v>
       </c>
       <c r="P15" s="38" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="Q15" s="38" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="R15" s="39" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="S15" s="67" t="s">
         <v>1</v>
@@ -4307,26 +4312,26 @@
         <v>SUS.Robot</v>
       </c>
       <c r="W15" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X15" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-15</v>
       </c>
       <c r="Y15" s="39" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="Z15" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA15" s="39" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="AB15" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC15" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD15" s="39" t="s">
         <v>1</v>
@@ -4337,19 +4342,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C16" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E16" s="71" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F16" s="74" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G16" s="52" t="s">
         <v>1</v>
@@ -4383,13 +4388,13 @@
         <v>SUS.Equipamento</v>
       </c>
       <c r="P16" s="38" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Q16" s="38" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="R16" s="39" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="S16" s="67" t="s">
         <v>1</v>
@@ -4407,26 +4412,26 @@
         <v>SUS.Equipamento</v>
       </c>
       <c r="W16" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X16" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-16</v>
       </c>
       <c r="Y16" s="39" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="Z16" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA16" s="39" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="AB16" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC16" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD16" s="39" t="s">
         <v>1</v>
@@ -4437,19 +4442,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C17" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E17" s="71" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G17" s="52" t="s">
         <v>1</v>
@@ -4483,13 +4488,13 @@
         <v>SUS.Dispositivo</v>
       </c>
       <c r="P17" s="38" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="Q17" s="38" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="R17" s="39" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="S17" s="67" t="s">
         <v>1</v>
@@ -4507,26 +4512,26 @@
         <v>SUS.Dispositivo</v>
       </c>
       <c r="W17" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X17" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-17</v>
       </c>
       <c r="Y17" s="39" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="Z17" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA17" s="39" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="AB17" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC17" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD17" s="39" t="s">
         <v>1</v>
@@ -4537,19 +4542,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C18" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E18" s="71" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F18" s="74" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G18" s="52" t="s">
         <v>1</v>
@@ -4583,13 +4588,13 @@
         <v>SUS.Instrumento</v>
       </c>
       <c r="P18" s="38" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="Q18" s="38" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="R18" s="39" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="S18" s="67" t="s">
         <v>1</v>
@@ -4607,26 +4612,26 @@
         <v>SUS.Instrumento</v>
       </c>
       <c r="W18" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X18" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-18</v>
       </c>
       <c r="Y18" s="39" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="Z18" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA18" s="39" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="AB18" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC18" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD18" s="39" t="s">
         <v>1</v>
@@ -4637,19 +4642,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C19" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E19" s="71" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G19" s="52" t="s">
         <v>1</v>
@@ -4683,13 +4688,13 @@
         <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="P19" s="38" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="Q19" s="38" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="R19" s="39" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="S19" s="67" t="s">
         <v>1</v>
@@ -4707,26 +4712,26 @@
         <v>SUS.Mobília.de.Saúde</v>
       </c>
       <c r="W19" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X19" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-19</v>
       </c>
       <c r="Y19" s="39" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Z19" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA19" s="39" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="AB19" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC19" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD19" s="39" t="s">
         <v>1</v>
@@ -4737,19 +4742,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C20" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E20" s="71" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F20" s="74" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G20" s="52" t="s">
         <v>1</v>
@@ -4783,13 +4788,13 @@
         <v>SUS.Mobília</v>
       </c>
       <c r="P20" s="38" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="Q20" s="38" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="R20" s="39" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="S20" s="67" t="s">
         <v>1</v>
@@ -4807,26 +4812,26 @@
         <v>SUS.Mobília</v>
       </c>
       <c r="W20" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X20" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-20</v>
       </c>
       <c r="Y20" s="39" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Z20" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA20" s="39" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="AB20" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC20" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD20" s="39" t="s">
         <v>1</v>
@@ -4837,19 +4842,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C21" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E21" s="71" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F21" s="74" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G21" s="52" t="s">
         <v>1</v>
@@ -4883,13 +4888,13 @@
         <v>SUS.Roupa</v>
       </c>
       <c r="P21" s="38" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q21" s="38" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="R21" s="39" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="S21" s="67" t="s">
         <v>1</v>
@@ -4907,26 +4912,26 @@
         <v>SUS.Roupa</v>
       </c>
       <c r="W21" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X21" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-21</v>
       </c>
       <c r="Y21" s="39" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Z21" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA21" s="39" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="AB21" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC21" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD21" s="39" t="s">
         <v>1</v>
@@ -4937,19 +4942,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="65" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C22" s="69" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="71" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E22" s="71" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F22" s="74" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G22" s="52" t="s">
         <v>1</v>
@@ -4983,13 +4988,13 @@
         <v>SUS.Alimentação</v>
       </c>
       <c r="P22" s="38" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Q22" s="38" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="R22" s="39" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="S22" s="67" t="s">
         <v>1</v>
@@ -5007,26 +5012,26 @@
         <v>SUS.Alimentação</v>
       </c>
       <c r="W22" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X22" s="42" t="str">
         <f t="shared" si="7"/>
         <v>Key-SUS-22</v>
       </c>
       <c r="Y22" s="39" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Z22" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AA22" s="39" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="AB22" s="50" t="s">
         <v>1</v>
       </c>
       <c r="AC22" s="40" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="AD22" s="39" t="s">
         <v>1</v>
@@ -5037,19 +5042,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E23" s="66" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="G23" s="62" t="s">
         <v>1</v>
@@ -5083,13 +5088,13 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P23" s="39" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="Q23" s="39" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="R23" s="39" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="S23" s="67" t="s">
         <v>1</v>
@@ -5107,7 +5112,7 @@
         <v>API Método</v>
       </c>
       <c r="W23" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X23" s="42" t="str">
         <f t="shared" si="7"/>
@@ -5137,19 +5142,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="65" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E24" s="66" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G24" s="62" t="s">
         <v>1</v>
@@ -5183,13 +5188,13 @@
         <v>Função Global</v>
       </c>
       <c r="P24" s="39" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q24" s="39" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="R24" s="39" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="S24" s="67" t="s">
         <v>1</v>
@@ -5207,7 +5212,7 @@
         <v>API Método</v>
       </c>
       <c r="W24" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X24" s="42" t="str">
         <f t="shared" si="7"/>
@@ -5237,19 +5242,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="65" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="F25" s="66" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G25" s="62" t="s">
         <v>1</v>
@@ -5283,13 +5288,13 @@
         <v>Função Local</v>
       </c>
       <c r="P25" s="39" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="Q25" s="39" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="R25" s="39" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="S25" s="67" t="s">
         <v>1</v>
@@ -5307,7 +5312,7 @@
         <v>API Método</v>
       </c>
       <c r="W25" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X25" s="42" t="str">
         <f t="shared" si="7"/>
@@ -5337,19 +5342,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="65" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E26" s="66" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="F26" s="66" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="G26" s="62" t="s">
         <v>1</v>
@@ -5383,13 +5388,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P26" s="39" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="Q26" s="39" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="R26" s="39" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="S26" s="67" t="s">
         <v>1</v>
@@ -5407,7 +5412,7 @@
         <v>API Método</v>
       </c>
       <c r="W26" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X26" s="42" t="str">
         <f t="shared" si="7"/>
@@ -5437,19 +5442,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="65" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E27" s="66" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="F27" s="66" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="G27" s="62" t="s">
         <v>1</v>
@@ -5483,13 +5488,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P27" s="39" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="Q27" s="39" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="R27" s="39" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="S27" s="67" t="s">
         <v>1</v>
@@ -5507,7 +5512,7 @@
         <v>API Método Visual</v>
       </c>
       <c r="W27" s="39" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X27" s="42" t="str">
         <f t="shared" si="7"/>
@@ -5777,10 +5782,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -5831,67 +5836,67 @@
         <v>24</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>48</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>48</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I1" s="21" t="s">
         <v>48</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>48</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="M1" s="20" t="s">
         <v>48</v>
       </c>
       <c r="N1" s="59" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O1" s="59" t="s">
         <v>48</v>
       </c>
       <c r="P1" s="59" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="59" t="s">
         <v>48</v>
       </c>
       <c r="R1" s="59" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="S1" s="59" t="s">
         <v>48</v>
       </c>
       <c r="T1" s="59" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="U1" s="59" t="s">
         <v>48</v>
       </c>
       <c r="V1" s="59" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="W1" s="59" t="s">
         <v>48</v>
@@ -5902,34 +5907,34 @@
         <v>2</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F2" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="L2" s="34" t="s">
         <v>1</v>
@@ -5973,34 +5978,34 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G3" s="55" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I3" s="35" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="L3" s="34" t="s">
         <v>1</v>
@@ -6044,34 +6049,34 @@
         <v>4</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="J4" s="34" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="L4" s="34" t="s">
         <v>1</v>
@@ -6115,34 +6120,34 @@
         <v>5</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="J5" s="34" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="L5" s="34" t="s">
         <v>1</v>
@@ -6186,28 +6191,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G6" s="55" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I6" s="55" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="J6" s="54" t="s">
         <v>1</v>
@@ -6220,7 +6225,7 @@
         <v>método.revit</v>
       </c>
       <c r="M6" s="57" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="N6" s="60" t="s">
         <v>1</v>
@@ -6258,28 +6263,28 @@
         <v>7</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D7" s="54" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G7" s="55" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I7" s="55" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="J7" s="54" t="s">
         <v>1</v>
@@ -6292,7 +6297,7 @@
         <v>método.revit</v>
       </c>
       <c r="M7" s="57" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="N7" s="60" t="s">
         <v>1</v>
@@ -6330,28 +6335,28 @@
         <v>8</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F8" s="54" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="55" t="s">
-        <v>241</v>
-      </c>
       <c r="H8" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I8" s="55" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="J8" s="54" t="s">
         <v>1</v>
@@ -6364,7 +6369,7 @@
         <v>método.revit</v>
       </c>
       <c r="M8" s="57" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="N8" s="60" t="s">
         <v>1</v>
@@ -6402,28 +6407,28 @@
         <v>9</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I9" s="55" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="J9" s="54" t="s">
         <v>1</v>
@@ -6436,7 +6441,7 @@
         <v>método.revit</v>
       </c>
       <c r="M9" s="57" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="N9" s="60" t="s">
         <v>1</v>
@@ -6474,28 +6479,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I10" s="55" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="J10" s="54" t="s">
         <v>1</v>
@@ -6508,7 +6513,7 @@
         <v>método.revit</v>
       </c>
       <c r="M10" s="57" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N10" s="60" t="s">
         <v>1</v>
